--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Desktop\02. 에디터 업무\05. 과제명 영문화\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FF1D5F-B216-4367-AA61-7775D54175F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA58C5B8-79B7-43BF-96F8-78C4AB541338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
   </bookViews>
   <sheets>
-    <sheet name="총괄" sheetId="1" r:id="rId1"/>
+    <sheet name="List" sheetId="1" r:id="rId1"/>
     <sheet name="DB1" sheetId="3" r:id="rId2"/>
     <sheet name="DB2" sheetId="4" r:id="rId3"/>
   </sheets>
@@ -8538,11 +8538,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12419,15 +12419,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:8" ht="42" thickBot="1">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>1815</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:8" ht="41.25">
       <c r="B3" s="4"/>
@@ -12932,7 +12932,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="33">
+    <row r="16" spans="1:8">
       <c r="A16" s="18" t="s">
         <v>895</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33">
+    <row r="26" spans="1:8">
       <c r="A26" s="18" t="s">
         <v>904</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="33">
+    <row r="110" spans="1:8">
       <c r="A110" s="18" t="s">
         <v>864</v>
       </c>
@@ -17051,7 +17051,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="33">
+    <row r="112" spans="1:8">
       <c r="A112" s="18" t="s">
         <v>870</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="33">
+    <row r="115" spans="1:8">
       <c r="A115" s="18" t="s">
         <v>875</v>
       </c>
@@ -17825,7 +17825,7 @@
         <v>46535</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="33">
+    <row r="130" spans="1:8">
       <c r="A130" s="18" t="s">
         <v>764</v>
       </c>
@@ -17868,7 +17868,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="33">
+    <row r="131" spans="1:8">
       <c r="A131" s="18" t="s">
         <v>767</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="33">
+    <row r="206" spans="1:8">
       <c r="A206" s="18" t="s">
         <v>964</v>
       </c>
@@ -21781,7 +21781,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="33">
+    <row r="222" spans="1:8">
       <c r="A222" s="23" t="s">
         <v>790</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="33">
+    <row r="236" spans="1:8">
       <c r="A236" s="23" t="s">
         <v>976</v>
       </c>
@@ -22899,7 +22899,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="33">
+    <row r="248" spans="1:8">
       <c r="A248" s="18" t="s">
         <v>809</v>
       </c>
@@ -23372,7 +23372,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="33">
+    <row r="259" spans="1:8">
       <c r="A259" s="18" t="s">
         <v>2229</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="33">
+    <row r="264" spans="1:8">
       <c r="A264" s="18" t="s">
         <v>752</v>
       </c>
@@ -25436,7 +25436,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="33">
+    <row r="307" spans="1:8">
       <c r="A307" s="23" t="s">
         <v>1914</v>
       </c>
@@ -26038,7 +26038,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="33">
+    <row r="321" spans="1:8">
       <c r="A321" s="23" t="s">
         <v>1929</v>
       </c>
@@ -26167,7 +26167,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="33">
+    <row r="324" spans="1:8">
       <c r="A324" s="23" t="s">
         <v>1933</v>
       </c>
@@ -26210,7 +26210,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="33">
+    <row r="325" spans="1:8">
       <c r="A325" s="23" t="s">
         <v>1934</v>
       </c>
@@ -26683,7 +26683,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="336" spans="1:8" ht="33">
+    <row r="336" spans="1:8">
       <c r="A336" s="23" t="s">
         <v>1948</v>
       </c>
@@ -27113,7 +27113,7 @@
         <v>46319</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="33">
+    <row r="346" spans="1:8">
       <c r="A346" s="23" t="s">
         <v>1951</v>
       </c>
@@ -50341,10 +50341,10 @@
       <c r="B56" s="7" t="s">
         <v>1115</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="51" t="s">
         <v>2387</v>
       </c>
-      <c r="G56" s="52" t="s">
+      <c r="G56" s="51" t="s">
         <v>2386</v>
       </c>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Desktop\02. 에디터 업무\05. 과제명 영문화\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA58C5B8-79B7-43BF-96F8-78C4AB541338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63678750-DA61-4369-AF3E-312255F64C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5194" uniqueCount="2388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5194" uniqueCount="2387">
   <si>
     <t>Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -8051,10 +8051,6 @@
   </si>
   <si>
     <t>Research for the Formulation of the 4th Basic Plan for Conservation of Natural Environment (2026–2035)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eoclogy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -19444,7 +19440,7 @@
       </c>
       <c r="E167" s="15" t="str">
         <f>VLOOKUP($A167,'DB1'!$C:$Q,14,0)</f>
-        <v>Eoclogy</v>
+        <v>Ecology</v>
       </c>
       <c r="F167" s="15" t="str">
         <f>VLOOKUP($A167,'DB1'!$C:$Q,15,0)</f>
@@ -37853,7 +37849,7 @@
         <v>Hong, Hyunjung</v>
       </c>
       <c r="P164" s="39" t="s">
-        <v>2364</v>
+        <v>1801</v>
       </c>
       <c r="Q164" s="45" t="s">
         <v>2264</v>
@@ -38026,7 +38022,7 @@
         <v>410</v>
       </c>
       <c r="N167" s="44" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="O167" s="35" t="str">
         <f>IFERROR(VLOOKUP($G167,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -38661,7 +38657,7 @@
       </c>
       <c r="M178" s="19"/>
       <c r="N178" s="42" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="O178" s="35" t="str">
         <f>IFERROR(VLOOKUP($G178,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -39375,7 +39371,7 @@
         <v>634</v>
       </c>
       <c r="N190" s="44" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="O190" s="35" t="str">
         <f>IFERROR(VLOOKUP($G190,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -39757,7 +39753,7 @@
         <v>666</v>
       </c>
       <c r="D197" s="19" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="E197" s="19"/>
       <c r="F197" s="19" t="s">
@@ -40489,7 +40485,7 @@
         <v>168</v>
       </c>
       <c r="N209" s="44" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="O209" s="35" t="str">
         <f>IFERROR(VLOOKUP($G209,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -40549,7 +40545,7 @@
         <v>47</v>
       </c>
       <c r="N210" s="42" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="O210" s="35" t="str">
         <f>IFERROR(VLOOKUP($G210,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -41021,7 +41017,7 @@
       </c>
       <c r="M218" s="29"/>
       <c r="N218" s="48" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="O218" s="35" t="str">
         <f>IFERROR(VLOOKUP($G218,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -41077,7 +41073,7 @@
       </c>
       <c r="M219" s="19"/>
       <c r="N219" s="48" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="O219" s="35" t="str">
         <f>IFERROR(VLOOKUP($G219,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -41430,7 +41426,7 @@
         <v>706</v>
       </c>
       <c r="N225" s="49" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="O225" s="35" t="str">
         <f>IFERROR(VLOOKUP($G225,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -41490,7 +41486,7 @@
         <v>709</v>
       </c>
       <c r="N226" s="47" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="O226" s="35" t="str">
         <f>IFERROR(VLOOKUP($G226,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -41550,7 +41546,7 @@
         <v>59</v>
       </c>
       <c r="N227" s="48" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="O227" s="35" t="str">
         <f>IFERROR(VLOOKUP($G227,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -42308,7 +42304,7 @@
         <v>1824</v>
       </c>
       <c r="N240" s="49" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="O240" s="35" t="str">
         <f>IFERROR(VLOOKUP($G240,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -45013,7 +45009,7 @@
         <v>350</v>
       </c>
       <c r="N288" s="48" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O288" s="35" t="str">
         <f>IFERROR(VLOOKUP($G288,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -45417,7 +45413,7 @@
         <v>59</v>
       </c>
       <c r="N295" s="48" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="O295" s="35" t="str">
         <f>IFERROR(VLOOKUP($G295,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -45871,7 +45867,7 @@
       </c>
       <c r="M303" s="19"/>
       <c r="N303" s="48" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="O303" s="35" t="str">
         <f>IFERROR(VLOOKUP($G303,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -46817,7 +46813,7 @@
       </c>
       <c r="M320" s="19"/>
       <c r="N320" s="48" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="O320" s="35" t="str">
         <f>IFERROR(VLOOKUP($G320,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -47535,7 +47531,7 @@
       </c>
       <c r="M333" s="19"/>
       <c r="N333" s="49" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="O333" s="35" t="str">
         <f>IFERROR(VLOOKUP($G333,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -48949,7 +48945,7 @@
       </c>
       <c r="M358" s="29"/>
       <c r="N358" s="41" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="O358" s="35" t="str">
         <f>IFERROR(VLOOKUP($G358,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -49171,7 +49167,7 @@
       </c>
       <c r="M362" s="29"/>
       <c r="N362" s="41" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="O362" s="35" t="str">
         <f>IFERROR(VLOOKUP($G362,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -50256,7 +50252,7 @@
         <v>1105</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>983</v>
@@ -50310,7 +50306,7 @@
         <v>1111</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>986</v>
@@ -50342,10 +50338,10 @@
         <v>1115</v>
       </c>
       <c r="F56" s="51" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G56" s="51" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="57" spans="1:9">

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Desktop\02. 에디터 업무\05. 과제명 영문화\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1636CB-8D35-4D93-8EE0-633C64087C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9ABCC1-0D4E-4CC5-89BA-58E24AFB1068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
   </bookViews>
   <sheets>
-    <sheet name="총괄" sheetId="1" r:id="rId1"/>
+    <sheet name="List" sheetId="1" r:id="rId1"/>
     <sheet name="DB1" sheetId="3" r:id="rId2"/>
     <sheet name="DB2" sheetId="4" r:id="rId3"/>
   </sheets>
@@ -8519,14 +8519,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12403,15 +12403,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:8" ht="42" thickBot="1">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>1814</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" ht="41.25">
       <c r="B3" s="4"/>
@@ -34024,7 +34024,7 @@
       <c r="P99" s="35" t="s">
         <v>1800</v>
       </c>
-      <c r="Q99" s="47" t="s">
+      <c r="Q99" s="46" t="s">
         <v>2163</v>
       </c>
       <c r="R99" s="35" t="str">
@@ -37839,7 +37839,7 @@
       <c r="P164" s="35" t="s">
         <v>2362</v>
       </c>
-      <c r="Q164" s="47" t="s">
+      <c r="Q164" s="46" t="s">
         <v>2263</v>
       </c>
       <c r="R164" s="35" t="str">
@@ -38480,7 +38480,7 @@
       <c r="P175" s="35" t="s">
         <v>2266</v>
       </c>
-      <c r="Q175" s="47" t="s">
+      <c r="Q175" s="46" t="s">
         <v>2264</v>
       </c>
       <c r="R175" s="35" t="str">
@@ -41413,7 +41413,7 @@
       <c r="M225" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="N225" s="48" t="s">
+      <c r="N225" s="47" t="s">
         <v>2371</v>
       </c>
       <c r="O225" s="35" t="str">
@@ -42291,7 +42291,7 @@
       <c r="M240" s="19" t="s">
         <v>1823</v>
       </c>
-      <c r="N240" s="48" t="s">
+      <c r="N240" s="47" t="s">
         <v>2374</v>
       </c>
       <c r="O240" s="35" t="str">
@@ -47086,7 +47086,7 @@
       <c r="P325" s="35" t="s">
         <v>1803</v>
       </c>
-      <c r="Q325" s="47" t="s">
+      <c r="Q325" s="46" t="s">
         <v>2288</v>
       </c>
       <c r="R325" s="35" t="str">
@@ -47518,7 +47518,7 @@
         <v>46387</v>
       </c>
       <c r="M333" s="19"/>
-      <c r="N333" s="48" t="s">
+      <c r="N333" s="47" t="s">
         <v>2379</v>
       </c>
       <c r="O333" s="35" t="str">

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Desktop\02. 에디터 업무\05. 과제명 영문화\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9ABCC1-0D4E-4CC5-89BA-58E24AFB1068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA1254-A608-459A-8E7A-B12BA8D7CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2390">
   <si>
     <t>Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -6011,10 +6011,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Measures for Adjusting Transport Fuel Prices and Using Tax Revenues to Promote the Transition to Zero-Emission Vehicles</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Assessment of Effectiveness and Policy Measures for Securing River Flood Buffer Spaces</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -8031,10 +8027,6 @@
   </si>
   <si>
     <t>Research for the Formulation of the 4th Basic Plan for Conservation of Natural Environment (2026–2035)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eoclogy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -8179,6 +8171,10 @@
   </si>
   <si>
     <t>A Study on Improving the Legal and Institutional Framework for Integrated Estuary Management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measures for Adjusting Transport Fuel Prices and Utilizing Tax Revenues to Promote the Transition to Zero-Emission Vehicles</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -12404,7 +12400,7 @@
     <row r="1" spans="1:8" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:8" ht="42" thickBot="1">
       <c r="B2" s="48" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -19428,7 +19424,7 @@
       </c>
       <c r="E167" s="15" t="str">
         <f>VLOOKUP($A167,'DB1'!$C:$Q,14,0)</f>
-        <v>Eoclogy</v>
+        <v>Ecology</v>
       </c>
       <c r="F167" s="15" t="str">
         <f>VLOOKUP($A167,'DB1'!$C:$Q,15,0)</f>
@@ -22344,7 +22340,7 @@
       </c>
       <c r="C235" s="15" t="str">
         <f>VLOOKUP($A235,'DB1'!$C:$Q,12,0)</f>
-        <v>Measures for Adjusting Transport Fuel Prices and Using Tax Revenues to Promote the Transition to Zero-Emission Vehicles</v>
+        <v>Measures for Adjusting Transport Fuel Prices and Utilizing Tax Revenues to Promote the Transition to Zero-Emission Vehicles</v>
       </c>
       <c r="D235" s="11" t="str">
         <f>VLOOKUP($A235,'DB1'!$C:$Q,13,0)</f>
@@ -22455,7 +22451,7 @@
     </row>
     <row r="238" spans="1:8" ht="33">
       <c r="A238" s="23" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B238" s="15" t="str" cm="1">
         <f t="array" ref="B238">_xlfn.IFS(
@@ -22498,7 +22494,7 @@
     </row>
     <row r="239" spans="1:8" ht="33">
       <c r="A239" s="23" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B239" s="15" t="str" cm="1">
         <f t="array" ref="B239">_xlfn.IFS(
@@ -22541,7 +22537,7 @@
     </row>
     <row r="240" spans="1:8" ht="33">
       <c r="A240" s="23" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B240" s="15" t="str" cm="1">
         <f t="array" ref="B240">_xlfn.IFS(
@@ -22584,7 +22580,7 @@
     </row>
     <row r="241" spans="1:8" ht="33">
       <c r="A241" s="23" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B241" s="15" t="str" cm="1">
         <f t="array" ref="B241">_xlfn.IFS(
@@ -22627,7 +22623,7 @@
     </row>
     <row r="242" spans="1:8" ht="33">
       <c r="A242" s="23" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B242" s="15" t="str" cm="1">
         <f t="array" ref="B242">_xlfn.IFS(
@@ -22670,7 +22666,7 @@
     </row>
     <row r="243" spans="1:8" ht="33">
       <c r="A243" s="23" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B243" s="15" t="str" cm="1">
         <f t="array" ref="B243">_xlfn.IFS(
@@ -23358,7 +23354,7 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259" s="18" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="B259" s="15" t="str" cm="1">
         <f t="array" ref="B259">_xlfn.IFS(
@@ -23659,7 +23655,7 @@
     </row>
     <row r="266" spans="1:8" ht="33">
       <c r="A266" s="18" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B266" s="15" t="str" cm="1">
         <f t="array" ref="B266">_xlfn.IFS(
@@ -23702,7 +23698,7 @@
     </row>
     <row r="267" spans="1:8" ht="33">
       <c r="A267" s="23" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B267" s="15" t="str" cm="1">
         <f t="array" ref="B267">_xlfn.IFS(
@@ -23745,7 +23741,7 @@
     </row>
     <row r="268" spans="1:8" ht="33">
       <c r="A268" s="23" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="B268" s="15" t="str" cm="1">
         <f t="array" ref="B268">_xlfn.IFS(
@@ -23788,7 +23784,7 @@
     </row>
     <row r="269" spans="1:8" ht="33">
       <c r="A269" s="23" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B269" s="15" t="str" cm="1">
         <f t="array" ref="B269">_xlfn.IFS(
@@ -23831,7 +23827,7 @@
     </row>
     <row r="270" spans="1:8" ht="33">
       <c r="A270" s="23" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B270" s="15" t="str" cm="1">
         <f t="array" ref="B270">_xlfn.IFS(
@@ -23874,7 +23870,7 @@
     </row>
     <row r="271" spans="1:8" ht="33">
       <c r="A271" s="23" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B271" s="15" t="str" cm="1">
         <f t="array" ref="B271">_xlfn.IFS(
@@ -23917,7 +23913,7 @@
     </row>
     <row r="272" spans="1:8" ht="49.5">
       <c r="A272" s="23" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B272" s="15" t="str" cm="1">
         <f t="array" ref="B272">_xlfn.IFS(
@@ -23960,7 +23956,7 @@
     </row>
     <row r="273" spans="1:8" ht="33">
       <c r="A273" s="23" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B273" s="15" t="str" cm="1">
         <f t="array" ref="B273">_xlfn.IFS(
@@ -24003,7 +23999,7 @@
     </row>
     <row r="274" spans="1:8" ht="33">
       <c r="A274" s="23" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B274" s="15" t="str" cm="1">
         <f t="array" ref="B274">_xlfn.IFS(
@@ -24046,7 +24042,7 @@
     </row>
     <row r="275" spans="1:8" ht="33">
       <c r="A275" s="23" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B275" s="15" t="str" cm="1">
         <f t="array" ref="B275">_xlfn.IFS(
@@ -24089,7 +24085,7 @@
     </row>
     <row r="276" spans="1:8" ht="33">
       <c r="A276" s="23" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B276" s="15" t="str" cm="1">
         <f t="array" ref="B276">_xlfn.IFS(
@@ -24132,7 +24128,7 @@
     </row>
     <row r="277" spans="1:8" ht="33">
       <c r="A277" s="23" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="B277" s="15" t="str" cm="1">
         <f t="array" ref="B277">_xlfn.IFS(
@@ -24175,7 +24171,7 @@
     </row>
     <row r="278" spans="1:8" ht="49.5">
       <c r="A278" s="23" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B278" s="15" t="str" cm="1">
         <f t="array" ref="B278">_xlfn.IFS(
@@ -24218,7 +24214,7 @@
     </row>
     <row r="279" spans="1:8" ht="33">
       <c r="A279" s="23" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="B279" s="15" t="str" cm="1">
         <f t="array" ref="B279">_xlfn.IFS(
@@ -24261,7 +24257,7 @@
     </row>
     <row r="280" spans="1:8" ht="33">
       <c r="A280" s="23" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="B280" s="15" t="str" cm="1">
         <f t="array" ref="B280">_xlfn.IFS(
@@ -24304,7 +24300,7 @@
     </row>
     <row r="281" spans="1:8" ht="33">
       <c r="A281" s="23" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B281" s="15" t="str" cm="1">
         <f t="array" ref="B281">_xlfn.IFS(
@@ -24347,7 +24343,7 @@
     </row>
     <row r="282" spans="1:8" ht="33">
       <c r="A282" s="23" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B282" s="15" t="str" cm="1">
         <f t="array" ref="B282">_xlfn.IFS(
@@ -24390,7 +24386,7 @@
     </row>
     <row r="283" spans="1:8" ht="33">
       <c r="A283" s="23" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B283" s="15" t="str" cm="1">
         <f t="array" ref="B283">_xlfn.IFS(
@@ -24433,7 +24429,7 @@
     </row>
     <row r="284" spans="1:8" ht="33">
       <c r="A284" s="23" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="B284" s="15" t="str" cm="1">
         <f t="array" ref="B284">_xlfn.IFS(
@@ -24476,7 +24472,7 @@
     </row>
     <row r="285" spans="1:8" ht="33">
       <c r="A285" s="23" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B285" s="15" t="str" cm="1">
         <f t="array" ref="B285">_xlfn.IFS(
@@ -24519,7 +24515,7 @@
     </row>
     <row r="286" spans="1:8" ht="33">
       <c r="A286" s="23" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B286" s="15" t="str" cm="1">
         <f t="array" ref="B286">_xlfn.IFS(
@@ -24562,7 +24558,7 @@
     </row>
     <row r="287" spans="1:8" ht="33">
       <c r="A287" s="23" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B287" s="15" t="str" cm="1">
         <f t="array" ref="B287">_xlfn.IFS(
@@ -24605,7 +24601,7 @@
     </row>
     <row r="288" spans="1:8" ht="33">
       <c r="A288" s="23" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B288" s="15" t="str" cm="1">
         <f t="array" ref="B288">_xlfn.IFS(
@@ -24648,7 +24644,7 @@
     </row>
     <row r="289" spans="1:8" ht="33">
       <c r="A289" s="23" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B289" s="15" t="str" cm="1">
         <f t="array" ref="B289">_xlfn.IFS(
@@ -24691,7 +24687,7 @@
     </row>
     <row r="290" spans="1:8" ht="33">
       <c r="A290" s="23" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="B290" s="15" t="str" cm="1">
         <f t="array" ref="B290">_xlfn.IFS(
@@ -24734,7 +24730,7 @@
     </row>
     <row r="291" spans="1:8" ht="33">
       <c r="A291" s="23" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B291" s="15" t="str" cm="1">
         <f t="array" ref="B291">_xlfn.IFS(
@@ -24777,7 +24773,7 @@
     </row>
     <row r="292" spans="1:8" ht="33">
       <c r="A292" s="23" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B292" s="15" t="str" cm="1">
         <f t="array" ref="B292">_xlfn.IFS(
@@ -24820,7 +24816,7 @@
     </row>
     <row r="293" spans="1:8" ht="33">
       <c r="A293" s="23" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B293" s="15" t="str" cm="1">
         <f t="array" ref="B293">_xlfn.IFS(
@@ -24863,7 +24859,7 @@
     </row>
     <row r="294" spans="1:8" ht="33">
       <c r="A294" s="23" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B294" s="15" t="str" cm="1">
         <f t="array" ref="B294">_xlfn.IFS(
@@ -24906,7 +24902,7 @@
     </row>
     <row r="295" spans="1:8" ht="33">
       <c r="A295" s="23" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B295" s="15" t="str" cm="1">
         <f t="array" ref="B295">_xlfn.IFS(
@@ -24949,7 +24945,7 @@
     </row>
     <row r="296" spans="1:8" ht="49.5">
       <c r="A296" s="23" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B296" s="15" t="str" cm="1">
         <f t="array" ref="B296">_xlfn.IFS(
@@ -24992,7 +24988,7 @@
     </row>
     <row r="297" spans="1:8" ht="33">
       <c r="A297" s="23" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="B297" s="15" t="str" cm="1">
         <f t="array" ref="B297">_xlfn.IFS(
@@ -25035,7 +25031,7 @@
     </row>
     <row r="298" spans="1:8" ht="33">
       <c r="A298" s="23" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="B298" s="15" t="str" cm="1">
         <f t="array" ref="B298">_xlfn.IFS(
@@ -25078,7 +25074,7 @@
     </row>
     <row r="299" spans="1:8" ht="33">
       <c r="A299" s="23" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B299" s="15" t="str" cm="1">
         <f t="array" ref="B299">_xlfn.IFS(
@@ -25121,7 +25117,7 @@
     </row>
     <row r="300" spans="1:8" ht="33">
       <c r="A300" s="23" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B300" s="15" t="str" cm="1">
         <f t="array" ref="B300">_xlfn.IFS(
@@ -25164,7 +25160,7 @@
     </row>
     <row r="301" spans="1:8" ht="33">
       <c r="A301" s="23" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B301" s="15" t="str" cm="1">
         <f t="array" ref="B301">_xlfn.IFS(
@@ -25207,7 +25203,7 @@
     </row>
     <row r="302" spans="1:8" ht="33">
       <c r="A302" s="23" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B302" s="15" t="str" cm="1">
         <f t="array" ref="B302">_xlfn.IFS(
@@ -25250,7 +25246,7 @@
     </row>
     <row r="303" spans="1:8" ht="33">
       <c r="A303" s="23" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B303" s="15" t="str" cm="1">
         <f t="array" ref="B303">_xlfn.IFS(
@@ -25293,7 +25289,7 @@
     </row>
     <row r="304" spans="1:8" ht="49.5">
       <c r="A304" s="23" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B304" s="15" t="str" cm="1">
         <f t="array" ref="B304">_xlfn.IFS(
@@ -25336,7 +25332,7 @@
     </row>
     <row r="305" spans="1:8" ht="33">
       <c r="A305" s="23" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B305" s="15" t="str" cm="1">
         <f t="array" ref="B305">_xlfn.IFS(
@@ -25379,7 +25375,7 @@
     </row>
     <row r="306" spans="1:8" ht="33">
       <c r="A306" s="23" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B306" s="15" t="str" cm="1">
         <f t="array" ref="B306">_xlfn.IFS(
@@ -25422,7 +25418,7 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="23" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B307" s="15" t="str" cm="1">
         <f t="array" ref="B307">_xlfn.IFS(
@@ -25465,7 +25461,7 @@
     </row>
     <row r="308" spans="1:8" ht="33">
       <c r="A308" s="23" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B308" s="15" t="str" cm="1">
         <f t="array" ref="B308">_xlfn.IFS(
@@ -25508,7 +25504,7 @@
     </row>
     <row r="309" spans="1:8" ht="33">
       <c r="A309" s="23" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B309" s="15" t="str" cm="1">
         <f t="array" ref="B309">_xlfn.IFS(
@@ -25551,7 +25547,7 @@
     </row>
     <row r="310" spans="1:8" ht="33">
       <c r="A310" s="23" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B310" s="15" t="str" cm="1">
         <f t="array" ref="B310">_xlfn.IFS(
@@ -25594,7 +25590,7 @@
     </row>
     <row r="311" spans="1:8" ht="33">
       <c r="A311" s="23" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B311" s="15" t="str" cm="1">
         <f t="array" ref="B311">_xlfn.IFS(
@@ -25637,7 +25633,7 @@
     </row>
     <row r="312" spans="1:8" ht="33">
       <c r="A312" s="23" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B312" s="15" t="str" cm="1">
         <f t="array" ref="B312">_xlfn.IFS(
@@ -25680,7 +25676,7 @@
     </row>
     <row r="313" spans="1:8" ht="33">
       <c r="A313" s="23" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B313" s="15" t="str" cm="1">
         <f t="array" ref="B313">_xlfn.IFS(
@@ -25723,7 +25719,7 @@
     </row>
     <row r="314" spans="1:8" ht="33">
       <c r="A314" s="23" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B314" s="15" t="str" cm="1">
         <f t="array" ref="B314">_xlfn.IFS(
@@ -25766,7 +25762,7 @@
     </row>
     <row r="315" spans="1:8" ht="33">
       <c r="A315" s="23" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B315" s="15" t="str" cm="1">
         <f t="array" ref="B315">_xlfn.IFS(
@@ -25809,7 +25805,7 @@
     </row>
     <row r="316" spans="1:8" ht="33">
       <c r="A316" s="23" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B316" s="15" t="str" cm="1">
         <f t="array" ref="B316">_xlfn.IFS(
@@ -25852,7 +25848,7 @@
     </row>
     <row r="317" spans="1:8" ht="33">
       <c r="A317" s="23" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B317" s="15" t="str" cm="1">
         <f t="array" ref="B317">_xlfn.IFS(
@@ -25895,7 +25891,7 @@
     </row>
     <row r="318" spans="1:8" ht="33">
       <c r="A318" s="23" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B318" s="15" t="str" cm="1">
         <f t="array" ref="B318">_xlfn.IFS(
@@ -25938,7 +25934,7 @@
     </row>
     <row r="319" spans="1:8" ht="33">
       <c r="A319" s="23" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B319" s="15" t="str" cm="1">
         <f t="array" ref="B319">_xlfn.IFS(
@@ -25981,7 +25977,7 @@
     </row>
     <row r="320" spans="1:8" ht="33">
       <c r="A320" s="23" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B320" s="15" t="str" cm="1">
         <f t="array" ref="B320">_xlfn.IFS(
@@ -26024,7 +26020,7 @@
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="23" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B321" s="15" t="str" cm="1">
         <f t="array" ref="B321">_xlfn.IFS(
@@ -26067,7 +26063,7 @@
     </row>
     <row r="322" spans="1:8" ht="33">
       <c r="A322" s="23" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B322" s="15" t="str" cm="1">
         <f t="array" ref="B322">_xlfn.IFS(
@@ -26110,7 +26106,7 @@
     </row>
     <row r="323" spans="1:8" ht="33">
       <c r="A323" s="23" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B323" s="15" t="str" cm="1">
         <f t="array" ref="B323">_xlfn.IFS(
@@ -26153,7 +26149,7 @@
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="23" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B324" s="15" t="str" cm="1">
         <f t="array" ref="B324">_xlfn.IFS(
@@ -26196,7 +26192,7 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="23" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B325" s="15" t="str" cm="1">
         <f t="array" ref="B325">_xlfn.IFS(
@@ -26239,7 +26235,7 @@
     </row>
     <row r="326" spans="1:8" ht="33">
       <c r="A326" s="23" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B326" s="15" t="str" cm="1">
         <f t="array" ref="B326">_xlfn.IFS(
@@ -26282,7 +26278,7 @@
     </row>
     <row r="327" spans="1:8" ht="33">
       <c r="A327" s="23" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B327" s="15" t="str" cm="1">
         <f t="array" ref="B327">_xlfn.IFS(
@@ -26325,7 +26321,7 @@
     </row>
     <row r="328" spans="1:8" ht="33">
       <c r="A328" s="23" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B328" s="15" t="str" cm="1">
         <f t="array" ref="B328">_xlfn.IFS(
@@ -26368,7 +26364,7 @@
     </row>
     <row r="329" spans="1:8" ht="33">
       <c r="A329" s="23" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B329" s="15" t="str" cm="1">
         <f t="array" ref="B329">_xlfn.IFS(
@@ -26411,7 +26407,7 @@
     </row>
     <row r="330" spans="1:8" ht="33">
       <c r="A330" s="23" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B330" s="15" t="str" cm="1">
         <f t="array" ref="B330">_xlfn.IFS(
@@ -26454,7 +26450,7 @@
     </row>
     <row r="331" spans="1:8" ht="33">
       <c r="A331" s="23" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B331" s="15" t="str" cm="1">
         <f t="array" ref="B331">_xlfn.IFS(
@@ -26497,7 +26493,7 @@
     </row>
     <row r="332" spans="1:8" ht="33">
       <c r="A332" s="23" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B332" s="15" t="str" cm="1">
         <f t="array" ref="B332">_xlfn.IFS(
@@ -26540,7 +26536,7 @@
     </row>
     <row r="333" spans="1:8" ht="33">
       <c r="A333" s="23" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B333" s="15" t="str" cm="1">
         <f t="array" ref="B333">_xlfn.IFS(
@@ -26583,7 +26579,7 @@
     </row>
     <row r="334" spans="1:8" ht="33">
       <c r="A334" s="23" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B334" s="15" t="str" cm="1">
         <f t="array" ref="B334">_xlfn.IFS(
@@ -26626,7 +26622,7 @@
     </row>
     <row r="335" spans="1:8" ht="33">
       <c r="A335" s="23" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B335" s="15" t="str" cm="1">
         <f t="array" ref="B335">_xlfn.IFS(
@@ -26669,7 +26665,7 @@
     </row>
     <row r="336" spans="1:8">
       <c r="A336" s="23" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B336" s="15" t="str" cm="1">
         <f t="array" ref="B336">_xlfn.IFS(
@@ -26712,7 +26708,7 @@
     </row>
     <row r="337" spans="1:8" ht="33">
       <c r="A337" s="23" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B337" s="15" t="str" cm="1">
         <f t="array" ref="B337">_xlfn.IFS(
@@ -26755,7 +26751,7 @@
     </row>
     <row r="338" spans="1:8" ht="49.5">
       <c r="A338" s="23" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B338" s="15" t="str" cm="1">
         <f t="array" ref="B338">_xlfn.IFS(
@@ -26798,7 +26794,7 @@
     </row>
     <row r="339" spans="1:8" ht="33">
       <c r="A339" s="23" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B339" s="15" t="str" cm="1">
         <f t="array" ref="B339">_xlfn.IFS(
@@ -26841,7 +26837,7 @@
     </row>
     <row r="340" spans="1:8" ht="33">
       <c r="A340" s="23" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B340" s="15" t="str" cm="1">
         <f t="array" ref="B340">_xlfn.IFS(
@@ -26884,7 +26880,7 @@
     </row>
     <row r="341" spans="1:8" ht="33">
       <c r="A341" s="23" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B341" s="15" t="str" cm="1">
         <f t="array" ref="B341">_xlfn.IFS(
@@ -26927,7 +26923,7 @@
     </row>
     <row r="342" spans="1:8" ht="33">
       <c r="A342" s="23" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B342" s="15" t="str" cm="1">
         <f t="array" ref="B342">_xlfn.IFS(
@@ -26970,7 +26966,7 @@
     </row>
     <row r="343" spans="1:8" ht="33">
       <c r="A343" s="23" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B343" s="15" t="str" cm="1">
         <f t="array" ref="B343">_xlfn.IFS(
@@ -27013,7 +27009,7 @@
     </row>
     <row r="344" spans="1:8" ht="33">
       <c r="A344" s="23" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B344" s="15" t="str" cm="1">
         <f t="array" ref="B344">_xlfn.IFS(
@@ -27056,7 +27052,7 @@
     </row>
     <row r="345" spans="1:8" ht="33">
       <c r="A345" s="23" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B345" s="15" t="str" cm="1">
         <f t="array" ref="B345">_xlfn.IFS(
@@ -27099,7 +27095,7 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="23" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B346" s="15" t="str" cm="1">
         <f t="array" ref="B346">_xlfn.IFS(
@@ -27142,7 +27138,7 @@
     </row>
     <row r="347" spans="1:8" ht="33">
       <c r="A347" s="23" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B347" s="15" t="str" cm="1">
         <f t="array" ref="B347">_xlfn.IFS(
@@ -27185,7 +27181,7 @@
     </row>
     <row r="348" spans="1:8" ht="33">
       <c r="A348" s="23" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B348" s="15" t="str" cm="1">
         <f t="array" ref="B348">_xlfn.IFS(
@@ -27228,7 +27224,7 @@
     </row>
     <row r="349" spans="1:8" ht="49.5">
       <c r="A349" s="32" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="B349" s="15" t="str" cm="1">
         <f t="array" ref="B349">_xlfn.IFS(
@@ -27271,7 +27267,7 @@
     </row>
     <row r="350" spans="1:8" ht="33">
       <c r="A350" s="32" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="B350" s="15" t="str" cm="1">
         <f t="array" ref="B350">_xlfn.IFS(
@@ -27314,7 +27310,7 @@
     </row>
     <row r="351" spans="1:8" ht="33">
       <c r="A351" s="32" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="B351" s="15" t="str" cm="1">
         <f t="array" ref="B351">_xlfn.IFS(
@@ -27357,7 +27353,7 @@
     </row>
     <row r="352" spans="1:8" ht="33">
       <c r="A352" s="32" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="B352" s="15" t="str" cm="1">
         <f t="array" ref="B352">_xlfn.IFS(
@@ -27400,7 +27396,7 @@
     </row>
     <row r="353" spans="1:8" ht="33">
       <c r="A353" s="32" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="B353" s="15" t="str" cm="1">
         <f t="array" ref="B353">_xlfn.IFS(
@@ -27443,7 +27439,7 @@
     </row>
     <row r="354" spans="1:8" ht="33">
       <c r="A354" s="32" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B354" s="15" t="str" cm="1">
         <f t="array" ref="B354">_xlfn.IFS(
@@ -27486,7 +27482,7 @@
     </row>
     <row r="355" spans="1:8" ht="33">
       <c r="A355" s="32" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B355" s="15" t="str" cm="1">
         <f t="array" ref="B355">_xlfn.IFS(
@@ -27529,7 +27525,7 @@
     </row>
     <row r="356" spans="1:8" ht="49.5">
       <c r="A356" s="32" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B356" s="15" t="str" cm="1">
         <f t="array" ref="B356">_xlfn.IFS(
@@ -27572,7 +27568,7 @@
     </row>
     <row r="357" spans="1:8" ht="33">
       <c r="A357" s="32" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="B357" s="15" t="str" cm="1">
         <f t="array" ref="B357">_xlfn.IFS(
@@ -27615,7 +27611,7 @@
     </row>
     <row r="358" spans="1:8" ht="33">
       <c r="A358" s="32" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="B358" s="15" t="str" cm="1">
         <f t="array" ref="B358">_xlfn.IFS(
@@ -27658,7 +27654,7 @@
     </row>
     <row r="359" spans="1:8" ht="49.5">
       <c r="A359" s="32" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="B359" s="15" t="str" cm="1">
         <f t="array" ref="B359">_xlfn.IFS(
@@ -27701,7 +27697,7 @@
     </row>
     <row r="360" spans="1:8" ht="33">
       <c r="A360" s="32" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B360" s="15" t="str" cm="1">
         <f t="array" ref="B360">_xlfn.IFS(
@@ -27744,7 +27740,7 @@
     </row>
     <row r="361" spans="1:8" ht="33">
       <c r="A361" s="32" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B361" s="15" t="str" cm="1">
         <f t="array" ref="B361">_xlfn.IFS(
@@ -27787,7 +27783,7 @@
     </row>
     <row r="362" spans="1:8" ht="33">
       <c r="A362" s="32" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B362" s="15" t="str" cm="1">
         <f t="array" ref="B362">_xlfn.IFS(
@@ -27830,7 +27826,7 @@
     </row>
     <row r="363" spans="1:8" ht="33">
       <c r="A363" s="32" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B363" s="15" t="str" cm="1">
         <f t="array" ref="B363">_xlfn.IFS(
@@ -27873,7 +27869,7 @@
     </row>
     <row r="364" spans="1:8" ht="33">
       <c r="A364" s="32" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B364" s="15" t="str" cm="1">
         <f t="array" ref="B364">_xlfn.IFS(
@@ -27916,7 +27912,7 @@
     </row>
     <row r="365" spans="1:8" ht="33">
       <c r="A365" s="32" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B365" s="15" t="str" cm="1">
         <f t="array" ref="B365">_xlfn.IFS(
@@ -27959,7 +27955,7 @@
     </row>
     <row r="366" spans="1:8" ht="33">
       <c r="A366" s="32" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B366" s="15" t="str" cm="1">
         <f t="array" ref="B366">_xlfn.IFS(
@@ -28002,7 +27998,7 @@
     </row>
     <row r="367" spans="1:8" ht="33">
       <c r="A367" s="32" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B367" s="15" t="str" cm="1">
         <f t="array" ref="B367">_xlfn.IFS(
@@ -28045,7 +28041,7 @@
     </row>
     <row r="368" spans="1:8" ht="33">
       <c r="A368" s="32" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B368" s="15" t="str" cm="1">
         <f t="array" ref="B368">_xlfn.IFS(
@@ -28284,7 +28280,7 @@
         <v>1614</v>
       </c>
       <c r="Q2" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R2" s="35" t="str">
         <f>IFERROR(VLOOKUP($I2,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -28344,7 +28340,7 @@
         <v>1614</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R3" s="35" t="str">
         <f>IFERROR(VLOOKUP($I3,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -28366,7 +28362,7 @@
         <v>35</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="E4" s="19"/>
       <c r="F4" s="19" t="s">
@@ -28394,7 +28390,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="O4" s="35" t="str">
         <f>IFERROR(VLOOKUP($G4,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -28404,7 +28400,7 @@
         <v>1622</v>
       </c>
       <c r="Q4" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R4" s="35" t="str">
         <f>IFERROR(VLOOKUP($I4,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -28461,7 +28457,7 @@
         <v>Son, Seungwoo</v>
       </c>
       <c r="P5" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q5" s="35" t="s">
         <v>1614</v>
@@ -28514,7 +28510,7 @@
         <v>74</v>
       </c>
       <c r="N6" s="40" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="O6" s="35" t="str">
         <f>IFERROR(VLOOKUP($G6,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -28524,7 +28520,7 @@
         <v>1619</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R6" s="35" t="str">
         <f>IFERROR(VLOOKUP($I6,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -28574,14 +28570,14 @@
         <v>59</v>
       </c>
       <c r="N7" s="40" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="O7" s="35" t="str">
         <f>IFERROR(VLOOKUP($G7,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Yuyoung</v>
       </c>
       <c r="P7" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q7" s="35" t="s">
         <v>1614</v>
@@ -28666,7 +28662,7 @@
         <v>76</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="19" t="s">
@@ -28694,14 +28690,14 @@
         <v>47</v>
       </c>
       <c r="N9" s="40" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="O9" s="35" t="str">
         <f>IFERROR(VLOOKUP($G9,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Son, Seungwoo</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q9" s="35" t="s">
         <v>1614</v>
@@ -28761,10 +28757,10 @@
         <v>Lee, MoungJin</v>
       </c>
       <c r="P10" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q10" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R10" s="35" t="str">
         <f>IFERROR(VLOOKUP($I10,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -28824,7 +28820,7 @@
         <v>1618</v>
       </c>
       <c r="Q11" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R11" s="35" t="str">
         <f>IFERROR(VLOOKUP($I11,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -28846,7 +28842,7 @@
         <v>105</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="19" t="s">
@@ -28874,7 +28870,7 @@
         <v>106</v>
       </c>
       <c r="N12" s="40" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="O12" s="35" t="str">
         <f>IFERROR(VLOOKUP($G12,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -28906,7 +28902,7 @@
         <v>895</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="19" t="s">
@@ -28988,14 +28984,14 @@
       </c>
       <c r="M14" s="19"/>
       <c r="N14" s="40" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="O14" s="35" t="str">
         <f>IFERROR(VLOOKUP($G14,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Yumi</v>
       </c>
       <c r="P14" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q14" s="35" t="s">
         <v>1618</v>
@@ -29020,7 +29016,7 @@
         <v>900</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19" t="s">
@@ -29046,17 +29042,17 @@
       </c>
       <c r="M15" s="19"/>
       <c r="N15" s="40" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="O15" s="35" t="str">
         <f>IFERROR(VLOOKUP($G15,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Chang Sug</v>
       </c>
       <c r="P15" s="35" t="s">
+        <v>2261</v>
+      </c>
+      <c r="Q15" s="35" t="s">
         <v>2262</v>
-      </c>
-      <c r="Q15" s="35" t="s">
-        <v>2263</v>
       </c>
       <c r="R15" s="35" t="str">
         <f>IFERROR(VLOOKUP($I15,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29106,7 +29102,7 @@
         <v>47</v>
       </c>
       <c r="N16" s="40" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="O16" s="35" t="str">
         <f>IFERROR(VLOOKUP($G16,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -29176,7 +29172,7 @@
         <v>1617</v>
       </c>
       <c r="Q17" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R17" s="35" t="str">
         <f>IFERROR(VLOOKUP($I17,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29291,7 +29287,7 @@
         <v>Son, Seungwoo</v>
       </c>
       <c r="P19" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q19" s="35" t="s">
         <v>1614</v>
@@ -29351,7 +29347,7 @@
         <v>Myeong, Soojeong</v>
       </c>
       <c r="P20" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q20" s="35"/>
       <c r="R20" s="35" t="str">
@@ -29407,7 +29403,7 @@
         <v>Park, Chang Sug</v>
       </c>
       <c r="P21" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q21" s="35" t="s">
         <v>1620</v>
@@ -29465,10 +29461,10 @@
         <v>Suh, Yang-won</v>
       </c>
       <c r="P22" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q22" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R22" s="35" t="str">
         <f>IFERROR(VLOOKUP($I22,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29584,7 +29580,7 @@
         <v>1621</v>
       </c>
       <c r="Q24" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="R24" s="35" t="str">
         <f>IFERROR(VLOOKUP($I24,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29635,13 +29631,13 @@
         <v>1754</v>
       </c>
       <c r="O25" s="35" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="P25" s="35" t="s">
         <v>1616</v>
       </c>
       <c r="Q25" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R25" s="35" t="str">
         <f>IFERROR(VLOOKUP($I25,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29747,17 +29743,17 @@
       </c>
       <c r="M27" s="19"/>
       <c r="N27" s="40" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="O27" s="35" t="str">
         <f>IFERROR(VLOOKUP($G27,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Jae-hyuck</v>
       </c>
       <c r="P27" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q27" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R27" s="35" t="str">
         <f>IFERROR(VLOOKUP($I27,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29805,17 +29801,17 @@
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="41" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="O28" s="35" t="str">
         <f>IFERROR(VLOOKUP($G28,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Kim, Taehyun </v>
       </c>
       <c r="P28" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q28" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R28" s="35" t="str">
         <f>IFERROR(VLOOKUP($I28,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -29870,7 +29866,7 @@
         <v>Jin, Daeyong</v>
       </c>
       <c r="P29" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q29" s="35"/>
       <c r="R29" s="35" t="str">
@@ -29926,7 +29922,7 @@
         <v>Park, Jun Hyun</v>
       </c>
       <c r="P30" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q30" s="35"/>
       <c r="R30" s="35" t="str">
@@ -29987,7 +29983,7 @@
         <v>1621</v>
       </c>
       <c r="Q31" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R31" s="35" t="str">
         <f>IFERROR(VLOOKUP($I31,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -30044,10 +30040,10 @@
         <v>Kim, Sungjin</v>
       </c>
       <c r="P32" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q32" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R32" s="35" t="str">
         <f>IFERROR(VLOOKUP($I32,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -30167,7 +30163,7 @@
         <v>1618</v>
       </c>
       <c r="Q34" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R34" s="35" t="str">
         <f>IFERROR(VLOOKUP($I34,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -30247,7 +30243,7 @@
         <v>143</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="E36" s="19"/>
       <c r="F36" s="19" t="s">
@@ -30275,7 +30271,7 @@
         <v>148</v>
       </c>
       <c r="N36" s="40" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="O36" s="35" t="str">
         <f>IFERROR(VLOOKUP($G36,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -30342,7 +30338,7 @@
         <v>Lee, Jeongeun</v>
       </c>
       <c r="P37" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q37" s="35" t="s">
         <v>1621</v>
@@ -30402,7 +30398,7 @@
         <v>Park, Chang Sug</v>
       </c>
       <c r="P38" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q38" s="35" t="s">
         <v>1622</v>
@@ -30462,7 +30458,7 @@
         <v>Son, Seungwoo</v>
       </c>
       <c r="P39" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q39" s="35" t="s">
         <v>1614</v>
@@ -30515,7 +30511,7 @@
         <v>172</v>
       </c>
       <c r="N40" s="40" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="O40" s="35" t="str">
         <f>IFERROR(VLOOKUP($G40,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -30525,7 +30521,7 @@
         <v>1617</v>
       </c>
       <c r="Q40" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R40" s="35" t="str">
         <f>IFERROR(VLOOKUP($I40,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -30547,7 +30543,7 @@
         <v>174</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="E41" s="19"/>
       <c r="F41" s="19" t="s">
@@ -30635,7 +30631,7 @@
         <v>168</v>
       </c>
       <c r="N42" s="41" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="O42" s="35" t="str">
         <f>IFERROR(VLOOKUP($G42,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -30645,7 +30641,7 @@
         <v>1614</v>
       </c>
       <c r="Q42" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R42" s="35" t="str">
         <f>IFERROR(VLOOKUP($I42,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -30815,7 +30811,7 @@
         <v>47</v>
       </c>
       <c r="N45" s="41" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="O45" s="35" t="str">
         <f>IFERROR(VLOOKUP($G45,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -30825,7 +30821,7 @@
         <v>1614</v>
       </c>
       <c r="Q45" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R45" s="35" t="str">
         <f>IFERROR(VLOOKUP($I45,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -30991,14 +30987,14 @@
         <v>47</v>
       </c>
       <c r="N48" s="40" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="O48" s="35" t="str">
         <f>IFERROR(VLOOKUP($G48,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Chang Sug</v>
       </c>
       <c r="P48" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q48" s="35"/>
       <c r="R48" s="35" t="str">
@@ -31052,10 +31048,10 @@
         <v>1643</v>
       </c>
       <c r="O49" s="35" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="P49" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q49" s="35" t="s">
         <v>1621</v>
@@ -31108,7 +31104,7 @@
         <v>47</v>
       </c>
       <c r="N50" s="40" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="O50" s="35" t="str">
         <f>IFERROR(VLOOKUP($G50,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -31176,7 +31172,7 @@
         <v>1617</v>
       </c>
       <c r="Q51" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R51" s="35" t="str">
         <f>IFERROR(VLOOKUP($I51,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -31226,7 +31222,7 @@
         <v>227</v>
       </c>
       <c r="N52" s="40" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="O52" s="35" t="str">
         <f>IFERROR(VLOOKUP($G52,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -31269,7 +31265,7 @@
         <v>732</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="J53" s="20">
         <v>15000000</v>
@@ -31282,17 +31278,17 @@
       </c>
       <c r="M53" s="19"/>
       <c r="N53" s="40" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O53" s="35" t="str">
         <f>IFERROR(VLOOKUP($G53,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Ju, Munsol </v>
       </c>
       <c r="P53" s="35" t="s">
+        <v>2161</v>
+      </c>
+      <c r="Q53" s="35" t="s">
         <v>2162</v>
-      </c>
-      <c r="Q53" s="35" t="s">
-        <v>2163</v>
       </c>
       <c r="R53" s="35" t="str">
         <f>IFERROR(VLOOKUP($I53,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -31327,7 +31323,7 @@
         <v>93</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="J54" s="20">
         <v>15000000</v>
@@ -31340,14 +31336,14 @@
       </c>
       <c r="M54" s="19"/>
       <c r="N54" s="40" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O54" s="35" t="str">
         <f>IFERROR(VLOOKUP($G54,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Oh, Myoungjin </v>
       </c>
       <c r="P54" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q54" s="35"/>
       <c r="R54" s="35" t="str">
@@ -31465,7 +31461,7 @@
         <v>Choi, Hee-Sun</v>
       </c>
       <c r="P56" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q56" s="35" t="s">
         <v>1614</v>
@@ -31576,7 +31572,7 @@
         <v>256</v>
       </c>
       <c r="N58" s="40" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="O58" s="35" t="str">
         <f>IFERROR(VLOOKUP($G58,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -31644,7 +31640,7 @@
         <v>1613</v>
       </c>
       <c r="Q59" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R59" s="35" t="str">
         <f>IFERROR(VLOOKUP($I59,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -31701,7 +31697,7 @@
         <v>Kim, Sungjin</v>
       </c>
       <c r="P60" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q60" s="35"/>
       <c r="R60" s="35" t="str">
@@ -31762,7 +31758,7 @@
         <v>1622</v>
       </c>
       <c r="Q61" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R61" s="35" t="str">
         <f>IFERROR(VLOOKUP($I61,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -31822,7 +31818,7 @@
         <v>1617</v>
       </c>
       <c r="Q62" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R62" s="35" t="str">
         <f>IFERROR(VLOOKUP($I62,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -31940,7 +31936,7 @@
         <v>1617</v>
       </c>
       <c r="Q64" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R64" s="35" t="str">
         <f>IFERROR(VLOOKUP($I64,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -31997,7 +31993,7 @@
         <v>Chung, Woo Hyun</v>
       </c>
       <c r="P65" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="Q65" s="35"/>
       <c r="R65" s="35" t="str">
@@ -32048,7 +32044,7 @@
         <v>292</v>
       </c>
       <c r="N66" s="40" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="O66" s="35" t="str">
         <f>IFERROR(VLOOKUP($G66,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32166,7 +32162,7 @@
         <v>292</v>
       </c>
       <c r="N68" s="40" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O68" s="35" t="str">
         <f>IFERROR(VLOOKUP($G68,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32176,7 +32172,7 @@
         <v>1619</v>
       </c>
       <c r="Q68" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R68" s="35" t="str">
         <f>IFERROR(VLOOKUP($I68,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32236,7 +32232,7 @@
         <v>1619</v>
       </c>
       <c r="Q69" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R69" s="35" t="str">
         <f>IFERROR(VLOOKUP($I69,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32409,7 +32405,7 @@
         <v>Yoon, Jeongho</v>
       </c>
       <c r="P72" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q72" s="35" t="s">
         <v>1618</v>
@@ -32462,7 +32458,7 @@
         <v>74</v>
       </c>
       <c r="N73" s="40" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="O73" s="35" t="str">
         <f>IFERROR(VLOOKUP($G73,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32472,7 +32468,7 @@
         <v>1619</v>
       </c>
       <c r="Q73" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R73" s="35" t="str">
         <f>IFERROR(VLOOKUP($I73,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32522,7 +32518,7 @@
         <v>334</v>
       </c>
       <c r="N74" s="40" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="O74" s="35" t="str">
         <f>IFERROR(VLOOKUP($G74,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32592,7 +32588,7 @@
         <v>1622</v>
       </c>
       <c r="Q75" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R75" s="35" t="str">
         <f>IFERROR(VLOOKUP($I75,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32614,7 +32610,7 @@
         <v>340</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="E76" s="19"/>
       <c r="F76" s="19" t="s">
@@ -32642,16 +32638,16 @@
         <v>344</v>
       </c>
       <c r="N76" s="40" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="O76" s="35" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="P76" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q76" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R76" s="35" t="str">
         <f>IFERROR(VLOOKUP($I76,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32701,7 +32697,7 @@
         <v>350</v>
       </c>
       <c r="N77" s="40" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="O77" s="35" t="str">
         <f>IFERROR(VLOOKUP($G77,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32711,7 +32707,7 @@
         <v>1620</v>
       </c>
       <c r="Q77" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R77" s="35" t="str">
         <f>IFERROR(VLOOKUP($I77,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32733,7 +32729,7 @@
         <v>352</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="E78" s="19"/>
       <c r="F78" s="19" t="s">
@@ -32761,17 +32757,17 @@
         <v>334</v>
       </c>
       <c r="N78" s="40" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="O78" s="35" t="str">
         <f>IFERROR(VLOOKUP($G78,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Song, Youngil</v>
       </c>
       <c r="P78" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q78" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R78" s="35" t="str">
         <f>IFERROR(VLOOKUP($I78,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32821,7 +32817,7 @@
         <v>334</v>
       </c>
       <c r="N79" s="40" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="O79" s="35" t="str">
         <f>IFERROR(VLOOKUP($G79,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32831,7 +32827,7 @@
         <v>1619</v>
       </c>
       <c r="Q79" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R79" s="35" t="str">
         <f>IFERROR(VLOOKUP($I79,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -32881,7 +32877,7 @@
         <v>334</v>
       </c>
       <c r="N80" s="40" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="O80" s="35" t="str">
         <f>IFERROR(VLOOKUP($G80,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -32941,17 +32937,17 @@
         <v>334</v>
       </c>
       <c r="N81" s="40" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="O81" s="35" t="str">
         <f>IFERROR(VLOOKUP($G81,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Chang, Hoon</v>
       </c>
       <c r="P81" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q81" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R81" s="35" t="str">
         <f>IFERROR(VLOOKUP($I81,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33001,7 +32997,7 @@
         <v>334</v>
       </c>
       <c r="N82" s="40" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="O82" s="35" t="str">
         <f>IFERROR(VLOOKUP($G82,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -33011,7 +33007,7 @@
         <v>1619</v>
       </c>
       <c r="Q82" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R82" s="35" t="str">
         <f>IFERROR(VLOOKUP($I82,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33033,7 +33029,7 @@
         <v>368</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="E83" s="19"/>
       <c r="F83" s="19" t="s">
@@ -33061,7 +33057,7 @@
         <v>334</v>
       </c>
       <c r="N83" s="40" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="O83" s="35" t="str">
         <f>IFERROR(VLOOKUP($G83,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -33071,7 +33067,7 @@
         <v>1615</v>
       </c>
       <c r="Q83" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R83" s="35" t="str">
         <f>IFERROR(VLOOKUP($I83,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33188,10 +33184,10 @@
         <v xml:space="preserve">Kim, Geunhan </v>
       </c>
       <c r="P85" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q85" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R85" s="35" t="str">
         <f>IFERROR(VLOOKUP($I85,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33311,7 +33307,7 @@
         <v>1617</v>
       </c>
       <c r="Q87" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R87" s="35" t="str">
         <f>IFERROR(VLOOKUP($I87,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33368,7 +33364,7 @@
         <v>Myeong, Soojeong</v>
       </c>
       <c r="P88" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q88" s="35" t="s">
         <v>1614</v>
@@ -33488,10 +33484,10 @@
         <v>Lee, Seungmin</v>
       </c>
       <c r="P90" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q90" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R90" s="35" t="str">
         <f>IFERROR(VLOOKUP($I90,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33726,7 +33722,7 @@
         <v>Cho, Hanna</v>
       </c>
       <c r="P94" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q94" s="35" t="s">
         <v>1620</v>
@@ -33751,7 +33747,7 @@
         <v>445</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="E95" s="19"/>
       <c r="F95" s="19" t="s">
@@ -33789,7 +33785,7 @@
         <v>1617</v>
       </c>
       <c r="Q95" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R95" s="35" t="str">
         <f>IFERROR(VLOOKUP($I95,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33846,10 +33842,10 @@
         <v>Myeong, Soojeong</v>
       </c>
       <c r="P96" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q96" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R96" s="35" t="str">
         <f>IFERROR(VLOOKUP($I96,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -33899,7 +33895,7 @@
         <v>350</v>
       </c>
       <c r="N97" s="40" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="O97" s="35" t="str">
         <f>IFERROR(VLOOKUP($G97,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34015,17 +34011,17 @@
       </c>
       <c r="M99" s="19"/>
       <c r="N99" s="40" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="O99" s="35" t="str">
         <f>IFERROR(VLOOKUP($G99,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Hong, Hyunjung</v>
       </c>
       <c r="P99" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q99" s="46" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R99" s="35" t="str">
         <f>IFERROR(VLOOKUP($I99,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -34080,7 +34076,7 @@
         <v>Lee, Jae-hyuck</v>
       </c>
       <c r="P100" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q100" s="35" t="s">
         <v>1620</v>
@@ -34105,7 +34101,7 @@
         <v>848</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E101" s="19"/>
       <c r="F101" s="19" t="s">
@@ -34131,7 +34127,7 @@
       </c>
       <c r="M101" s="19"/>
       <c r="N101" s="40" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="O101" s="35" t="str">
         <f>IFERROR(VLOOKUP($G101,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34199,7 +34195,7 @@
         <v>1619</v>
       </c>
       <c r="Q102" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R102" s="35" t="str">
         <f>IFERROR(VLOOKUP($I102,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -34221,7 +34217,7 @@
         <v>855</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E103" s="19"/>
       <c r="F103" s="19" t="s">
@@ -34247,7 +34243,7 @@
       </c>
       <c r="M103" s="19"/>
       <c r="N103" s="41" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="O103" s="35" t="str">
         <f>IFERROR(VLOOKUP($G103,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34257,7 +34253,7 @@
         <v>1617</v>
       </c>
       <c r="Q103" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R103" s="35" t="str">
         <f>IFERROR(VLOOKUP($I103,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -34305,7 +34301,7 @@
       </c>
       <c r="M104" s="19"/>
       <c r="N104" s="40" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="O104" s="35" t="str">
         <f>IFERROR(VLOOKUP($G104,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34363,7 +34359,7 @@
       </c>
       <c r="M105" s="19"/>
       <c r="N105" s="40" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="O105" s="35" t="str">
         <f>IFERROR(VLOOKUP($G105,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34373,7 +34369,7 @@
         <v>1618</v>
       </c>
       <c r="Q105" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R105" s="35" t="str">
         <f>IFERROR(VLOOKUP($I105,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -34428,7 +34424,7 @@
         <v>Chung, Woo Hyun</v>
       </c>
       <c r="P106" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q106" s="35" t="s">
         <v>1622</v>
@@ -34482,7 +34478,7 @@
         <v>1742</v>
       </c>
       <c r="O107" s="35" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="P107" s="35" t="s">
         <v>1615</v>
@@ -34544,7 +34540,7 @@
         <v>1616</v>
       </c>
       <c r="Q108" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R108" s="35" t="str">
         <f>IFERROR(VLOOKUP($I108,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -34566,7 +34562,7 @@
         <v>870</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="E109" s="19"/>
       <c r="F109" s="19" t="s">
@@ -34592,7 +34588,7 @@
       </c>
       <c r="M109" s="19"/>
       <c r="N109" s="40" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="O109" s="35" t="str">
         <f>IFERROR(VLOOKUP($G109,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34624,7 +34620,7 @@
         <v>872</v>
       </c>
       <c r="D110" s="19" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="E110" s="19"/>
       <c r="F110" s="19" t="s">
@@ -34650,7 +34646,7 @@
       </c>
       <c r="M110" s="19"/>
       <c r="N110" s="41" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="O110" s="35" t="str">
         <f>IFERROR(VLOOKUP($G110,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34718,7 +34714,7 @@
         <v>1616</v>
       </c>
       <c r="Q111" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R111" s="35" t="str">
         <f>IFERROR(VLOOKUP($I111,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -34769,7 +34765,7 @@
         <v>1745</v>
       </c>
       <c r="O112" s="35" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="P112" s="35" t="s">
         <v>1615</v>
@@ -34830,7 +34826,7 @@
         <v>Kim, Sungjin</v>
       </c>
       <c r="P113" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q113" s="35" t="s">
         <v>1616</v>
@@ -34883,7 +34879,7 @@
         <v>410</v>
       </c>
       <c r="N114" s="40" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="O114" s="35" t="str">
         <f>IFERROR(VLOOKUP($G114,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -34953,7 +34949,7 @@
         <v>1617</v>
       </c>
       <c r="Q115" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R115" s="35" t="str">
         <f>IFERROR(VLOOKUP($I115,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -35033,7 +35029,7 @@
         <v>960</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="E117" s="19"/>
       <c r="F117" s="19" t="s">
@@ -35066,10 +35062,10 @@
         <v>Kang, Taek Goo</v>
       </c>
       <c r="P117" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q117" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R117" s="35" t="str">
         <f>IFERROR(VLOOKUP($I117,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -35117,7 +35113,7 @@
       </c>
       <c r="M118" s="19"/>
       <c r="N118" s="40" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="O118" s="35" t="str">
         <f>IFERROR(VLOOKUP($G118,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -35242,7 +35238,7 @@
         <v>Kim, Sungjin</v>
       </c>
       <c r="P120" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q120" s="35"/>
       <c r="R120" s="35" t="str">
@@ -35419,7 +35415,7 @@
         <v>1613</v>
       </c>
       <c r="Q123" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R123" s="35" t="str">
         <f>IFERROR(VLOOKUP($I123,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -35479,7 +35475,7 @@
         <v>1618</v>
       </c>
       <c r="Q124" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R124" s="35" t="str">
         <f>IFERROR(VLOOKUP($I124,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -35589,14 +35585,14 @@
         <v>59</v>
       </c>
       <c r="N126" s="40" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="O126" s="35" t="str">
         <f>IFERROR(VLOOKUP($G126,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Yuyoung</v>
       </c>
       <c r="P126" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q126" s="35" t="s">
         <v>1614</v>
@@ -35828,7 +35824,7 @@
         <v>Son, Seungwoo</v>
       </c>
       <c r="P130" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q130" s="35" t="s">
         <v>1614</v>
@@ -35888,7 +35884,7 @@
         <v>Park, Taeho</v>
       </c>
       <c r="P131" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="Q131" s="35"/>
       <c r="R131" s="35" t="str">
@@ -35946,7 +35942,7 @@
         <v xml:space="preserve">Song, Jiyoon </v>
       </c>
       <c r="P132" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q132" s="35"/>
       <c r="R132" s="35" t="str">
@@ -35969,7 +35965,7 @@
         <v>473</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="E133" s="19"/>
       <c r="F133" s="19" t="s">
@@ -35997,7 +35993,7 @@
         <v>47</v>
       </c>
       <c r="N133" s="40" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="O133" s="35" t="str">
         <f>IFERROR(VLOOKUP($G133,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -36062,7 +36058,7 @@
         <v>Lee, Sangbum</v>
       </c>
       <c r="P134" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="Q134" s="35" t="s">
         <v>1618</v>
@@ -36115,7 +36111,7 @@
         <v>47</v>
       </c>
       <c r="N135" s="40" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="O135" s="35" t="str">
         <f>IFERROR(VLOOKUP($G135,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -36183,7 +36179,7 @@
         <v>1614</v>
       </c>
       <c r="Q136" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R136" s="35" t="str">
         <f>IFERROR(VLOOKUP($I136,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36240,7 +36236,7 @@
         <v>Choi, Hyungsik</v>
       </c>
       <c r="P137" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q137" s="35" t="s">
         <v>1621</v>
@@ -36293,7 +36289,7 @@
         <v>168</v>
       </c>
       <c r="N138" s="41" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="O138" s="35" t="str">
         <f>IFERROR(VLOOKUP($G138,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -36303,7 +36299,7 @@
         <v>1614</v>
       </c>
       <c r="Q138" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R138" s="35" t="str">
         <f>IFERROR(VLOOKUP($I138,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36338,7 +36334,7 @@
         <v>382</v>
       </c>
       <c r="I139" s="19" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="J139" s="20">
         <v>80742060</v>
@@ -36353,7 +36349,7 @@
         <v>172</v>
       </c>
       <c r="N139" s="40" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="O139" s="35" t="str">
         <f>IFERROR(VLOOKUP($G139,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -36363,7 +36359,7 @@
         <v>1617</v>
       </c>
       <c r="Q139" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R139" s="35" t="str">
         <f>IFERROR(VLOOKUP($I139,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36420,10 +36416,10 @@
         <v>Bae, Hyun-Joo</v>
       </c>
       <c r="P140" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q140" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R140" s="35" t="str">
         <f>IFERROR(VLOOKUP($I140,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36483,7 +36479,7 @@
         <v>1621</v>
       </c>
       <c r="Q141" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R141" s="35" t="str">
         <f>IFERROR(VLOOKUP($I141,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36543,7 +36539,7 @@
         <v>1621</v>
       </c>
       <c r="Q142" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R142" s="35" t="str">
         <f>IFERROR(VLOOKUP($I142,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36603,7 +36599,7 @@
         <v>1614</v>
       </c>
       <c r="Q143" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R143" s="35" t="str">
         <f>IFERROR(VLOOKUP($I143,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36663,7 +36659,7 @@
         <v>1618</v>
       </c>
       <c r="Q144" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R144" s="35" t="str">
         <f>IFERROR(VLOOKUP($I144,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36720,10 +36716,10 @@
         <v xml:space="preserve">Kim, Geunhan </v>
       </c>
       <c r="P145" s="35" t="s">
+        <v>2262</v>
+      </c>
+      <c r="Q145" s="35" t="s">
         <v>2263</v>
-      </c>
-      <c r="Q145" s="35" t="s">
-        <v>2264</v>
       </c>
       <c r="R145" s="35" t="str">
         <f>IFERROR(VLOOKUP($I145,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36773,17 +36769,17 @@
         <v>350</v>
       </c>
       <c r="N146" s="41" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="O146" s="35" t="str">
         <f>IFERROR(VLOOKUP($G146,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Koo, Kyung Ah </v>
       </c>
       <c r="P146" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q146" s="35" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="R146" s="35" t="str">
         <f>IFERROR(VLOOKUP($I146,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -36953,17 +36949,17 @@
         <v>387</v>
       </c>
       <c r="N149" s="40" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="O149" s="35" t="str">
         <f>IFERROR(VLOOKUP($G149,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Song, Jiyoon </v>
       </c>
       <c r="P149" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q149" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R149" s="35" t="str">
         <f>IFERROR(VLOOKUP($I149,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -37013,7 +37009,7 @@
         <v>618</v>
       </c>
       <c r="N150" s="40" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="O150" s="35" t="str">
         <f>IFERROR(VLOOKUP($G150,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -37045,7 +37041,7 @@
         <v>681</v>
       </c>
       <c r="D151" s="19" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="E151" s="19"/>
       <c r="F151" s="19" t="s">
@@ -37073,14 +37069,14 @@
         <v>387</v>
       </c>
       <c r="N151" s="40" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="O151" s="35" t="str">
         <f>IFERROR(VLOOKUP($G151,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Lee, Seungsoo </v>
       </c>
       <c r="P151" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q151" s="35"/>
       <c r="R151" s="35" t="str">
@@ -37094,7 +37090,7 @@
     </row>
     <row r="152" spans="1:19" ht="18" customHeight="1">
       <c r="A152" s="18" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B152" s="18" t="s">
         <v>836</v>
@@ -37129,7 +37125,7 @@
       </c>
       <c r="M152" s="19"/>
       <c r="N152" s="40" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="O152" s="35" t="str">
         <f>IFERROR(VLOOKUP($G152,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -37152,7 +37148,7 @@
     </row>
     <row r="153" spans="1:19" ht="18" customHeight="1">
       <c r="A153" s="18" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B153" s="18" t="s">
         <v>836</v>
@@ -37210,7 +37206,7 @@
     </row>
     <row r="154" spans="1:19" ht="18" customHeight="1">
       <c r="A154" s="18" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B154" s="18" t="s">
         <v>836</v>
@@ -37255,7 +37251,7 @@
         <v>1617</v>
       </c>
       <c r="Q154" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R154" s="35" t="str">
         <f>IFERROR(VLOOKUP($I154,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -37268,7 +37264,7 @@
     </row>
     <row r="155" spans="1:19" ht="18" customHeight="1">
       <c r="A155" s="18" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B155" s="18" t="s">
         <v>836</v>
@@ -37277,7 +37273,7 @@
         <v>933</v>
       </c>
       <c r="D155" s="19" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E155" s="19"/>
       <c r="F155" s="19" t="s">
@@ -37326,7 +37322,7 @@
     </row>
     <row r="156" spans="1:19" ht="18" customHeight="1">
       <c r="A156" s="18" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B156" s="18" t="s">
         <v>21</v>
@@ -37366,10 +37362,10 @@
         <v>1692</v>
       </c>
       <c r="O156" s="35" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="P156" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q156" s="35"/>
       <c r="R156" s="35" t="str">
@@ -37383,7 +37379,7 @@
     </row>
     <row r="157" spans="1:19" ht="18" customHeight="1">
       <c r="A157" s="18" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B157" s="18" t="s">
         <v>21</v>
@@ -37441,7 +37437,7 @@
     </row>
     <row r="158" spans="1:19" ht="18" customHeight="1">
       <c r="A158" s="18" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B158" s="18" t="s">
         <v>21</v>
@@ -37501,7 +37497,7 @@
     </row>
     <row r="159" spans="1:19" ht="18" customHeight="1">
       <c r="A159" s="18" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B159" s="18" t="s">
         <v>21</v>
@@ -37559,7 +37555,7 @@
     </row>
     <row r="160" spans="1:19" ht="18" customHeight="1">
       <c r="A160" s="18" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B160" s="18" t="s">
         <v>21</v>
@@ -37617,7 +37613,7 @@
     </row>
     <row r="161" spans="1:19" ht="18" customHeight="1">
       <c r="A161" s="18" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B161" s="18" t="s">
         <v>21</v>
@@ -37677,7 +37673,7 @@
     </row>
     <row r="162" spans="1:19" ht="18" customHeight="1">
       <c r="A162" s="18" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B162" s="18" t="s">
         <v>21</v>
@@ -37714,7 +37710,7 @@
         <v>556</v>
       </c>
       <c r="N162" s="40" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="O162" s="35" t="str">
         <f>IFERROR(VLOOKUP($G162,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -37735,7 +37731,7 @@
     </row>
     <row r="163" spans="1:19" ht="18" customHeight="1">
       <c r="A163" s="18" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B163" s="18" t="s">
         <v>21</v>
@@ -37793,7 +37789,7 @@
     </row>
     <row r="164" spans="1:19" ht="18" customHeight="1">
       <c r="A164" s="18" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B164" s="18" t="s">
         <v>21</v>
@@ -37830,17 +37826,17 @@
         <v>47</v>
       </c>
       <c r="N164" s="40" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="O164" s="35" t="str">
         <f>IFERROR(VLOOKUP($G164,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Hong, Hyunjung</v>
       </c>
       <c r="P164" s="35" t="s">
-        <v>2362</v>
+        <v>1799</v>
       </c>
       <c r="Q164" s="46" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R164" s="35" t="str">
         <f>IFERROR(VLOOKUP($I164,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -37853,7 +37849,7 @@
     </row>
     <row r="165" spans="1:19" ht="18" customHeight="1">
       <c r="A165" s="18" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B165" s="18" t="s">
         <v>21</v>
@@ -37897,10 +37893,10 @@
         <v>Lee, Byungkwon</v>
       </c>
       <c r="P165" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="Q165" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R165" s="35" t="str">
         <f>IFERROR(VLOOKUP($I165,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -37913,7 +37909,7 @@
     </row>
     <row r="166" spans="1:19" ht="18" customHeight="1">
       <c r="A166" s="18" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B166" s="18" t="s">
         <v>21</v>
@@ -37960,7 +37956,7 @@
         <v>1615</v>
       </c>
       <c r="Q166" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R166" s="35" t="str">
         <f>IFERROR(VLOOKUP($I166,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -37973,7 +37969,7 @@
     </row>
     <row r="167" spans="1:19" ht="18" customHeight="1">
       <c r="A167" s="18" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B167" s="18" t="s">
         <v>21</v>
@@ -38010,7 +38006,7 @@
         <v>410</v>
       </c>
       <c r="N167" s="41" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="O167" s="35" t="str">
         <f>IFERROR(VLOOKUP($G167,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -38031,7 +38027,7 @@
     </row>
     <row r="168" spans="1:19" ht="18" customHeight="1">
       <c r="A168" s="18" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B168" s="18" t="s">
         <v>21</v>
@@ -38091,7 +38087,7 @@
     </row>
     <row r="169" spans="1:19" ht="18" customHeight="1">
       <c r="A169" s="18" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B169" s="18" t="s">
         <v>21</v>
@@ -38151,7 +38147,7 @@
     </row>
     <row r="170" spans="1:19" ht="18" customHeight="1">
       <c r="A170" s="18" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B170" s="18" t="s">
         <v>21</v>
@@ -38209,7 +38205,7 @@
     </row>
     <row r="171" spans="1:19" ht="18" customHeight="1">
       <c r="A171" s="18" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B171" s="32" t="s">
         <v>21</v>
@@ -38225,13 +38221,13 @@
         <v>236</v>
       </c>
       <c r="G171" s="32" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H171" s="29" t="s">
         <v>208</v>
       </c>
       <c r="I171" s="29" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="J171" s="33">
         <v>161000000</v>
@@ -38246,13 +38242,13 @@
         <v>47</v>
       </c>
       <c r="N171" s="40" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="O171" s="35" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="P171" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q171" s="35"/>
       <c r="R171" s="35" t="str">
@@ -38266,7 +38262,7 @@
     </row>
     <row r="172" spans="1:19" ht="18" customHeight="1">
       <c r="A172" s="18" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B172" s="18" t="s">
         <v>836</v>
@@ -38308,7 +38304,7 @@
         <v>Choi, Kwanghun</v>
       </c>
       <c r="P172" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q172" s="35"/>
       <c r="R172" s="35" t="str">
@@ -38322,7 +38318,7 @@
     </row>
     <row r="173" spans="1:19" ht="18" customHeight="1">
       <c r="A173" s="18" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B173" s="18" t="s">
         <v>836</v>
@@ -38364,7 +38360,7 @@
         <v>Park, Jun Hyun</v>
       </c>
       <c r="P173" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q173" s="35"/>
       <c r="R173" s="35" t="str">
@@ -38378,7 +38374,7 @@
     </row>
     <row r="174" spans="1:19" ht="18" customHeight="1">
       <c r="A174" s="18" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B174" s="18" t="s">
         <v>836</v>
@@ -38413,7 +38409,7 @@
       </c>
       <c r="M174" s="19"/>
       <c r="N174" s="40" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="O174" s="35" t="str">
         <f>IFERROR(VLOOKUP($G174,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -38436,7 +38432,7 @@
     </row>
     <row r="175" spans="1:19" ht="18" customHeight="1">
       <c r="A175" s="18" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B175" s="18" t="s">
         <v>836</v>
@@ -38478,10 +38474,10 @@
         <v>Kim, Jongho</v>
       </c>
       <c r="P175" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="Q175" s="46" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R175" s="35" t="str">
         <f>IFERROR(VLOOKUP($I175,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -38494,7 +38490,7 @@
     </row>
     <row r="176" spans="1:19" ht="18" customHeight="1">
       <c r="A176" s="18" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B176" s="18" t="s">
         <v>836</v>
@@ -38539,7 +38535,7 @@
         <v>1621</v>
       </c>
       <c r="Q176" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R176" s="35" t="str">
         <f>IFERROR(VLOOKUP($I176,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -38552,7 +38548,7 @@
     </row>
     <row r="177" spans="1:19" ht="18" customHeight="1">
       <c r="A177" s="18" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B177" s="18" t="s">
         <v>836</v>
@@ -38594,10 +38590,10 @@
         <v xml:space="preserve">Song, Jiyoon </v>
       </c>
       <c r="P177" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q177" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R177" s="35" t="str">
         <f>IFERROR(VLOOKUP($I177,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -38610,7 +38606,7 @@
     </row>
     <row r="178" spans="1:19" ht="18" customHeight="1">
       <c r="A178" s="18" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B178" s="18" t="s">
         <v>836</v>
@@ -38645,7 +38641,7 @@
       </c>
       <c r="M178" s="19"/>
       <c r="N178" s="40" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="O178" s="35" t="str">
         <f>IFERROR(VLOOKUP($G178,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -38668,7 +38664,7 @@
     </row>
     <row r="179" spans="1:19" ht="18" customHeight="1">
       <c r="A179" s="18" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B179" s="18" t="s">
         <v>836</v>
@@ -38690,7 +38686,7 @@
         <v>32</v>
       </c>
       <c r="I179" s="19" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="J179" s="20">
         <v>40000000</v>
@@ -38703,7 +38699,7 @@
       </c>
       <c r="M179" s="19"/>
       <c r="N179" s="40" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="O179" s="35" t="str">
         <f>IFERROR(VLOOKUP($G179,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -38713,7 +38709,7 @@
         <v>1620</v>
       </c>
       <c r="Q179" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R179" s="35" t="str">
         <f>IFERROR(VLOOKUP($I179,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -38726,7 +38722,7 @@
     </row>
     <row r="180" spans="1:19" ht="18" customHeight="1">
       <c r="A180" s="18" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B180" s="18" t="s">
         <v>21</v>
@@ -38748,7 +38744,7 @@
         <v>198</v>
       </c>
       <c r="I180" s="19" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="J180" s="20">
         <v>90909090</v>
@@ -38770,7 +38766,7 @@
         <v>Lee, Jeongho</v>
       </c>
       <c r="P180" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q180" s="35"/>
       <c r="R180" s="35" t="str">
@@ -38784,7 +38780,7 @@
     </row>
     <row r="181" spans="1:19" ht="18" customHeight="1">
       <c r="A181" s="18" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B181" s="18" t="s">
         <v>21</v>
@@ -38844,7 +38840,7 @@
     </row>
     <row r="182" spans="1:19" ht="18" customHeight="1">
       <c r="A182" s="18" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B182" s="18" t="s">
         <v>21</v>
@@ -38891,7 +38887,7 @@
         <v>1617</v>
       </c>
       <c r="Q182" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R182" s="35" t="str">
         <f>IFERROR(VLOOKUP($I182,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -38904,7 +38900,7 @@
     </row>
     <row r="183" spans="1:19" ht="18" customHeight="1">
       <c r="A183" s="18" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B183" s="32" t="s">
         <v>21</v>
@@ -38948,7 +38944,7 @@
         <v>Son, Seungwoo</v>
       </c>
       <c r="P183" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q183" s="35" t="s">
         <v>1614</v>
@@ -38964,7 +38960,7 @@
     </row>
     <row r="184" spans="1:19" ht="18" customHeight="1">
       <c r="A184" s="18" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B184" s="18" t="s">
         <v>21</v>
@@ -39022,7 +39018,7 @@
     </row>
     <row r="185" spans="1:19" ht="18" customHeight="1">
       <c r="A185" s="18" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B185" s="18" t="s">
         <v>21</v>
@@ -39069,7 +39065,7 @@
         <v>1617</v>
       </c>
       <c r="Q185" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R185" s="35" t="str">
         <f>IFERROR(VLOOKUP($I185,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -39082,7 +39078,7 @@
     </row>
     <row r="186" spans="1:19" ht="18" customHeight="1">
       <c r="A186" s="18" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B186" s="18" t="s">
         <v>21</v>
@@ -39126,7 +39122,7 @@
         <v>Son, Seungwoo</v>
       </c>
       <c r="P186" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q186" s="35" t="s">
         <v>1614</v>
@@ -39142,7 +39138,7 @@
     </row>
     <row r="187" spans="1:19" ht="18" customHeight="1">
       <c r="A187" s="18" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>21</v>
@@ -39189,7 +39185,7 @@
         <v>1613</v>
       </c>
       <c r="Q187" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R187" s="35" t="str">
         <f>IFERROR(VLOOKUP($I187,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -39202,7 +39198,7 @@
     </row>
     <row r="188" spans="1:19" ht="18" customHeight="1">
       <c r="A188" s="18" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B188" s="18" t="s">
         <v>21</v>
@@ -39246,10 +39242,10 @@
         <v xml:space="preserve">Moon, Jongwoo </v>
       </c>
       <c r="P188" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q188" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R188" s="35" t="str">
         <f>IFERROR(VLOOKUP($I188,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -39262,7 +39258,7 @@
     </row>
     <row r="189" spans="1:19" ht="18" customHeight="1">
       <c r="A189" s="18" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B189" s="18" t="s">
         <v>21</v>
@@ -39322,7 +39318,7 @@
     </row>
     <row r="190" spans="1:19" ht="18" customHeight="1">
       <c r="A190" s="18" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B190" s="18" t="s">
         <v>21</v>
@@ -39331,7 +39327,7 @@
         <v>633</v>
       </c>
       <c r="D190" s="19" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="E190" s="19"/>
       <c r="F190" s="19" t="s">
@@ -39359,14 +39355,14 @@
         <v>634</v>
       </c>
       <c r="N190" s="41" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="O190" s="35" t="str">
         <f>IFERROR(VLOOKUP($G190,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Chung, Woo Hyun</v>
       </c>
       <c r="P190" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="Q190" s="35"/>
       <c r="R190" s="35" t="str">
@@ -39380,7 +39376,7 @@
     </row>
     <row r="191" spans="1:19" ht="18" customHeight="1">
       <c r="A191" s="18" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B191" s="18" t="s">
         <v>21</v>
@@ -39438,7 +39434,7 @@
     </row>
     <row r="192" spans="1:19" ht="18" customHeight="1">
       <c r="A192" s="18" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B192" s="18" t="s">
         <v>21</v>
@@ -39447,7 +39443,7 @@
         <v>648</v>
       </c>
       <c r="D192" s="19" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="E192" s="19"/>
       <c r="F192" s="19" t="s">
@@ -39496,7 +39492,7 @@
     </row>
     <row r="193" spans="1:19" ht="18" customHeight="1">
       <c r="A193" s="18" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B193" s="18" t="s">
         <v>727</v>
@@ -39505,7 +39501,7 @@
         <v>776</v>
       </c>
       <c r="D193" s="19" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="E193" s="19"/>
       <c r="F193" s="19" t="s">
@@ -39541,7 +39537,7 @@
         <v>1618</v>
       </c>
       <c r="Q193" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R193" s="35" t="str">
         <f>IFERROR(VLOOKUP($I193,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -39554,7 +39550,7 @@
     </row>
     <row r="194" spans="1:19" ht="18" customHeight="1">
       <c r="A194" s="18" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B194" s="18" t="s">
         <v>727</v>
@@ -39589,14 +39585,14 @@
       </c>
       <c r="M194" s="19"/>
       <c r="N194" s="40" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="O194" s="35" t="str">
         <f>IFERROR(VLOOKUP($G194,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Yuyoung</v>
       </c>
       <c r="P194" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q194" s="35" t="s">
         <v>1614</v>
@@ -39612,7 +39608,7 @@
     </row>
     <row r="195" spans="1:19" ht="18" customHeight="1">
       <c r="A195" s="18" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B195" s="18" t="s">
         <v>21</v>
@@ -39656,7 +39652,7 @@
         <v>Hyun, Yunjung</v>
       </c>
       <c r="P195" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q195" s="35" t="s">
         <v>1617</v>
@@ -39672,7 +39668,7 @@
     </row>
     <row r="196" spans="1:19" ht="18" customHeight="1">
       <c r="A196" s="18" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B196" s="18" t="s">
         <v>21</v>
@@ -39732,7 +39728,7 @@
     </row>
     <row r="197" spans="1:19" ht="18" customHeight="1">
       <c r="A197" s="18" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B197" s="18" t="s">
         <v>21</v>
@@ -39741,7 +39737,7 @@
         <v>666</v>
       </c>
       <c r="D197" s="19" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="E197" s="19"/>
       <c r="F197" s="19" t="s">
@@ -39776,10 +39772,10 @@
         <v>Kang, Taek Goo</v>
       </c>
       <c r="P197" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q197" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R197" s="35" t="str">
         <f>IFERROR(VLOOKUP($I197,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -39792,7 +39788,7 @@
     </row>
     <row r="198" spans="1:19" ht="18" customHeight="1">
       <c r="A198" s="18" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B198" s="18" t="s">
         <v>21</v>
@@ -39850,7 +39846,7 @@
     </row>
     <row r="199" spans="1:19" ht="18" customHeight="1">
       <c r="A199" s="18" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B199" s="32" t="s">
         <v>21</v>
@@ -39908,7 +39904,7 @@
     </row>
     <row r="200" spans="1:19" ht="18" customHeight="1">
       <c r="A200" s="18" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B200" s="32" t="s">
         <v>21</v>
@@ -39966,7 +39962,7 @@
     </row>
     <row r="201" spans="1:19" ht="18" customHeight="1">
       <c r="A201" s="18" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B201" s="18" t="s">
         <v>21</v>
@@ -40026,7 +40022,7 @@
     </row>
     <row r="202" spans="1:19" ht="18" customHeight="1">
       <c r="A202" s="18" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B202" s="18" t="s">
         <v>953</v>
@@ -40035,7 +40031,7 @@
         <v>963</v>
       </c>
       <c r="D202" s="19" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="E202" s="19"/>
       <c r="F202" s="19" t="s">
@@ -40084,7 +40080,7 @@
     </row>
     <row r="203" spans="1:19" ht="18" customHeight="1">
       <c r="A203" s="18" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B203" s="18" t="s">
         <v>953</v>
@@ -40093,7 +40089,7 @@
         <v>964</v>
       </c>
       <c r="D203" s="19" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="E203" s="19"/>
       <c r="F203" s="19" t="s">
@@ -40140,7 +40136,7 @@
     </row>
     <row r="204" spans="1:19" ht="18" customHeight="1">
       <c r="A204" s="18" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B204" s="18" t="s">
         <v>953</v>
@@ -40149,7 +40145,7 @@
         <v>965</v>
       </c>
       <c r="D204" s="19" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="E204" s="19"/>
       <c r="F204" s="19" t="s">
@@ -40185,7 +40181,7 @@
         <v>1622</v>
       </c>
       <c r="Q204" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R204" s="35" t="str">
         <f>IFERROR(VLOOKUP($I204,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40198,7 +40194,7 @@
     </row>
     <row r="205" spans="1:19" ht="18" customHeight="1">
       <c r="A205" s="18" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B205" s="18" t="s">
         <v>21</v>
@@ -40207,7 +40203,7 @@
         <v>670</v>
       </c>
       <c r="D205" s="19" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="E205" s="19"/>
       <c r="F205" s="19" t="s">
@@ -40242,7 +40238,7 @@
         <v>Lee, Jeongeun</v>
       </c>
       <c r="P205" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q205" s="35" t="s">
         <v>1621</v>
@@ -40258,7 +40254,7 @@
     </row>
     <row r="206" spans="1:19" ht="18" customHeight="1">
       <c r="A206" s="18" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B206" s="18" t="s">
         <v>21</v>
@@ -40267,7 +40263,7 @@
         <v>673</v>
       </c>
       <c r="D206" s="19" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="E206" s="19"/>
       <c r="F206" s="19" t="s">
@@ -40316,7 +40312,7 @@
     </row>
     <row r="207" spans="1:19" ht="18" customHeight="1">
       <c r="A207" s="18" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B207" s="18" t="s">
         <v>21</v>
@@ -40325,7 +40321,7 @@
         <v>672</v>
       </c>
       <c r="D207" s="19" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E207" s="19"/>
       <c r="F207" s="19" t="s">
@@ -40353,17 +40349,17 @@
         <v>148</v>
       </c>
       <c r="N207" s="40" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="O207" s="35" t="str">
         <f>IFERROR(VLOOKUP($G207,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Suh, Yang-won</v>
       </c>
       <c r="P207" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q207" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R207" s="35" t="str">
         <f>IFERROR(VLOOKUP($I207,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40376,7 +40372,7 @@
     </row>
     <row r="208" spans="1:19" ht="18" customHeight="1">
       <c r="A208" s="18" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B208" s="18" t="s">
         <v>21</v>
@@ -40385,7 +40381,7 @@
         <v>675</v>
       </c>
       <c r="D208" s="19" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E208" s="19"/>
       <c r="F208" s="19" t="s">
@@ -40423,7 +40419,7 @@
         <v>1621</v>
       </c>
       <c r="Q208" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R208" s="35" t="str">
         <f>IFERROR(VLOOKUP($I208,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40436,7 +40432,7 @@
     </row>
     <row r="209" spans="1:19" ht="18" customHeight="1">
       <c r="A209" s="18" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B209" s="18" t="s">
         <v>21</v>
@@ -40473,7 +40469,7 @@
         <v>168</v>
       </c>
       <c r="N209" s="41" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="O209" s="35" t="str">
         <f>IFERROR(VLOOKUP($G209,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -40483,7 +40479,7 @@
         <v>1614</v>
       </c>
       <c r="Q209" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R209" s="35" t="str">
         <f>IFERROR(VLOOKUP($I209,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40496,7 +40492,7 @@
     </row>
     <row r="210" spans="1:19" ht="18" customHeight="1">
       <c r="A210" s="18" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B210" s="18" t="s">
         <v>21</v>
@@ -40505,7 +40501,7 @@
         <v>678</v>
       </c>
       <c r="D210" s="19" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="E210" s="19"/>
       <c r="F210" s="19" t="s">
@@ -40533,7 +40529,7 @@
         <v>47</v>
       </c>
       <c r="N210" s="40" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="O210" s="35" t="str">
         <f>IFERROR(VLOOKUP($G210,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -40554,7 +40550,7 @@
     </row>
     <row r="211" spans="1:19" ht="18" customHeight="1">
       <c r="A211" s="18" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B211" s="18" t="s">
         <v>21</v>
@@ -40563,7 +40559,7 @@
         <v>679</v>
       </c>
       <c r="D211" s="19" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="E211" s="19"/>
       <c r="F211" s="19" t="s">
@@ -40598,7 +40594,7 @@
         <v>Gong, Sungyong</v>
       </c>
       <c r="P211" s="35" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="Q211" s="35" t="s">
         <v>1615</v>
@@ -40614,7 +40610,7 @@
     </row>
     <row r="212" spans="1:19" ht="18" customHeight="1">
       <c r="A212" s="18" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B212" s="23" t="s">
         <v>21</v>
@@ -40623,7 +40619,7 @@
         <v>682</v>
       </c>
       <c r="D212" s="42" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="E212" s="19"/>
       <c r="F212" s="19" t="s">
@@ -40716,10 +40712,10 @@
         <v>Yoon, Jeongho</v>
       </c>
       <c r="P213" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q213" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="R213" s="35" t="str">
         <f>IFERROR(VLOOKUP($I213,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40741,7 +40737,7 @@
         <v>685</v>
       </c>
       <c r="D214" s="42" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="E214" s="19"/>
       <c r="F214" s="19" t="s">
@@ -40799,7 +40795,7 @@
         <v>691</v>
       </c>
       <c r="D215" s="29" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="E215" s="29"/>
       <c r="F215" s="29" t="s">
@@ -40834,10 +40830,10 @@
         <v>Lee, Who-Seung</v>
       </c>
       <c r="P215" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q215" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R215" s="35" t="str">
         <f>IFERROR(VLOOKUP($I215,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40894,10 +40890,10 @@
         <v>Kim, Yumi</v>
       </c>
       <c r="P216" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q216" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R216" s="35" t="str">
         <f>IFERROR(VLOOKUP($I216,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40954,10 +40950,10 @@
         <v>Chang, Hoon</v>
       </c>
       <c r="P217" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q217" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="R217" s="35" t="str">
         <f>IFERROR(VLOOKUP($I217,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -40979,7 +40975,7 @@
         <v>784</v>
       </c>
       <c r="D218" s="29" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="E218" s="29"/>
       <c r="F218" s="29" t="s">
@@ -40992,7 +40988,7 @@
         <v>425</v>
       </c>
       <c r="I218" s="29" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="J218" s="33">
         <v>3000000</v>
@@ -41005,14 +41001,14 @@
       </c>
       <c r="M218" s="29"/>
       <c r="N218" s="43" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="O218" s="35" t="str">
         <f>IFERROR(VLOOKUP($G218,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Sungwoon</v>
       </c>
       <c r="P218" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q218" s="35"/>
       <c r="R218" s="35" t="str">
@@ -41061,17 +41057,17 @@
       </c>
       <c r="M219" s="19"/>
       <c r="N219" s="43" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="O219" s="35" t="str">
         <f>IFERROR(VLOOKUP($G219,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Sung, Kyungmin </v>
       </c>
       <c r="P219" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q219" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="R219" s="35" t="str">
         <f>IFERROR(VLOOKUP($I219,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41126,10 +41122,10 @@
         <v>Lee, Ji-Young</v>
       </c>
       <c r="P220" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q220" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R220" s="35" t="str">
         <f>IFERROR(VLOOKUP($I220,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41177,16 +41173,16 @@
       </c>
       <c r="M221" s="19"/>
       <c r="N221" s="43" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="O221" s="35" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="P221" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q221" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R221" s="35" t="str">
         <f>IFERROR(VLOOKUP($I221,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41234,17 +41230,17 @@
       </c>
       <c r="M222" s="19"/>
       <c r="N222" s="43" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="O222" s="35" t="str">
         <f>IFERROR(VLOOKUP($G222,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Shin, Dong Won</v>
       </c>
       <c r="P222" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q222" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R222" s="35" t="str">
         <f>IFERROR(VLOOKUP($I222,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41301,10 +41297,10 @@
         <v>Kim, Sungjin</v>
       </c>
       <c r="P223" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q223" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R223" s="35" t="str">
         <f>IFERROR(VLOOKUP($I223,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41361,10 +41357,10 @@
         <v>Lee, Jeongeun</v>
       </c>
       <c r="P224" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q224" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R224" s="35" t="str">
         <f>IFERROR(VLOOKUP($I224,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41414,17 +41410,17 @@
         <v>706</v>
       </c>
       <c r="N225" s="47" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="O225" s="35" t="str">
         <f>IFERROR(VLOOKUP($G225,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Koo, Kyung Ah </v>
       </c>
       <c r="P225" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q225" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R225" s="35" t="str">
         <f>IFERROR(VLOOKUP($I225,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41474,17 +41470,17 @@
         <v>709</v>
       </c>
       <c r="N226" s="43" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="O226" s="35" t="str">
         <f>IFERROR(VLOOKUP($G226,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Who-Seung</v>
       </c>
       <c r="P226" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q226" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R226" s="35" t="str">
         <f>IFERROR(VLOOKUP($I226,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41534,17 +41530,17 @@
         <v>59</v>
       </c>
       <c r="N227" s="43" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="O227" s="35" t="str">
         <f>IFERROR(VLOOKUP($G227,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Yuyoung</v>
       </c>
       <c r="P227" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q227" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R227" s="35" t="str">
         <f>IFERROR(VLOOKUP($I227,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41566,7 +41562,7 @@
         <v>713</v>
       </c>
       <c r="D228" s="29" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="E228" s="29"/>
       <c r="F228" s="29" t="s">
@@ -41601,10 +41597,10 @@
         <v>Shin, Dong Won</v>
       </c>
       <c r="P228" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q228" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R228" s="35" t="str">
         <f>IFERROR(VLOOKUP($I228,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41661,10 +41657,10 @@
         <v>Yi, Youngjae</v>
       </c>
       <c r="P229" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q229" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R229" s="35" t="str">
         <f>IFERROR(VLOOKUP($I229,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41714,14 +41710,14 @@
         <v>722</v>
       </c>
       <c r="N230" s="43" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="O230" s="35" t="str">
         <f>IFERROR(VLOOKUP($G230,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Han, Haejin</v>
       </c>
       <c r="P230" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q230" s="35"/>
       <c r="R230" s="35" t="str">
@@ -41772,17 +41768,17 @@
         <v>719</v>
       </c>
       <c r="N231" s="43" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="O231" s="35" t="str">
         <f>IFERROR(VLOOKUP($G231,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Oh, Myoungjin </v>
       </c>
       <c r="P231" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q231" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R231" s="35" t="str">
         <f>IFERROR(VLOOKUP($I231,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41830,17 +41826,17 @@
       </c>
       <c r="M232" s="19"/>
       <c r="N232" s="43" t="s">
-        <v>1796</v>
+        <v>2389</v>
       </c>
       <c r="O232" s="35" t="str">
         <f>IFERROR(VLOOKUP($G232,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Hahn, Jinseok</v>
       </c>
       <c r="P232" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q232" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R232" s="35" t="str">
         <f>IFERROR(VLOOKUP($I232,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41888,17 +41884,17 @@
       </c>
       <c r="M233" s="19"/>
       <c r="N233" s="43" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="O233" s="35" t="str">
         <f>IFERROR(VLOOKUP($G233,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Mikyoung</v>
       </c>
       <c r="P233" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q233" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R233" s="35" t="str">
         <f>IFERROR(VLOOKUP($I233,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41927,7 +41923,7 @@
         <v>129</v>
       </c>
       <c r="G234" s="23" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H234" s="19" t="s">
         <v>198</v>
@@ -41955,10 +41951,10 @@
         <v>Han, Daeho</v>
       </c>
       <c r="P234" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q234" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="R234" s="35" t="str">
         <f>IFERROR(VLOOKUP($I234,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -41975,14 +41971,14 @@
         <v>727</v>
       </c>
       <c r="C235" s="23" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="D235" s="42" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E235" s="19"/>
       <c r="F235" s="19" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="G235" s="23" t="s">
         <v>1295</v>
@@ -42004,17 +42000,17 @@
       </c>
       <c r="M235" s="19"/>
       <c r="N235" s="43" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="O235" s="35" t="str">
         <f>IFERROR(VLOOKUP($G235,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Yun, Seokhwan</v>
       </c>
       <c r="P235" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q235" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R235" s="35" t="str">
         <f>IFERROR(VLOOKUP($I235,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42031,14 +42027,14 @@
         <v>727</v>
       </c>
       <c r="C236" s="23" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="D236" s="42" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E236" s="19"/>
       <c r="F236" s="19" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="G236" s="23" t="s">
         <v>1605</v>
@@ -42060,17 +42056,17 @@
       </c>
       <c r="M236" s="19"/>
       <c r="N236" s="43" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="O236" s="35" t="str">
         <f>IFERROR(VLOOKUP($G236,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Song, Seulki</v>
       </c>
       <c r="P236" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q236" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R236" s="35" t="str">
         <f>IFERROR(VLOOKUP($I236,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42087,10 +42083,10 @@
         <v>21</v>
       </c>
       <c r="C237" s="23" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="D237" s="42" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E237" s="19"/>
       <c r="F237" s="19" t="s">
@@ -42115,20 +42111,20 @@
         <v>46180</v>
       </c>
       <c r="M237" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N237" s="43" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="O237" s="35" t="str">
         <f>IFERROR(VLOOKUP($G237,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Jeongeun</v>
       </c>
       <c r="P237" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q237" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R237" s="35" t="str">
         <f>IFERROR(VLOOKUP($I237,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42145,10 +42141,10 @@
         <v>21</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="D238" s="42" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="E238" s="19"/>
       <c r="F238" s="19" t="s">
@@ -42173,20 +42169,20 @@
         <v>46180</v>
       </c>
       <c r="M238" s="19" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="N238" s="43" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="O238" s="35" t="str">
         <f>IFERROR(VLOOKUP($G238,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Hee-Sun</v>
       </c>
       <c r="P238" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q238" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R238" s="35" t="str">
         <f>IFERROR(VLOOKUP($I238,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42203,10 +42199,10 @@
         <v>21</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="D239" s="42" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="E239" s="19"/>
       <c r="F239" s="19" t="s">
@@ -42231,20 +42227,20 @@
         <v>46179</v>
       </c>
       <c r="M239" s="19" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="N239" s="43" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="O239" s="35" t="str">
         <f>IFERROR(VLOOKUP($G239,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Who-Seung</v>
       </c>
       <c r="P239" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q239" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="R239" s="35" t="str">
         <f>IFERROR(VLOOKUP($I239,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42261,10 +42257,10 @@
         <v>21</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="D240" s="42" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="E240" s="19"/>
       <c r="F240" s="19" t="s">
@@ -42289,20 +42285,20 @@
         <v>46038</v>
       </c>
       <c r="M240" s="19" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="N240" s="47" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="O240" s="35" t="str">
         <f>IFERROR(VLOOKUP($G240,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Koo, Kyung Ah </v>
       </c>
       <c r="P240" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q240" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R240" s="35" t="str">
         <f>IFERROR(VLOOKUP($I240,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42322,7 +42318,7 @@
         <v>161</v>
       </c>
       <c r="D241" s="19" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="E241" s="19"/>
       <c r="F241" s="19" t="s">
@@ -42348,17 +42344,17 @@
       </c>
       <c r="M241" s="29"/>
       <c r="N241" s="40" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="O241" s="35" t="str">
         <f>IFERROR(VLOOKUP($G241,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Chang Sug</v>
       </c>
       <c r="P241" s="35" t="s">
+        <v>2261</v>
+      </c>
+      <c r="Q241" s="35" t="s">
         <v>2262</v>
-      </c>
-      <c r="Q241" s="35" t="s">
-        <v>2263</v>
       </c>
       <c r="R241" s="35" t="str">
         <f>IFERROR(VLOOKUP($I241,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42404,14 +42400,14 @@
       </c>
       <c r="M242" s="44"/>
       <c r="N242" s="40" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="O242" s="35" t="str">
         <f>IFERROR(VLOOKUP($G242,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Jun Hyun</v>
       </c>
       <c r="P242" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q242" s="35"/>
       <c r="R242" s="35" t="str">
@@ -42432,7 +42428,7 @@
         <v>803</v>
       </c>
       <c r="D243" s="19" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="E243" s="19"/>
       <c r="F243" s="19" t="s">
@@ -42458,17 +42454,17 @@
       </c>
       <c r="M243" s="44"/>
       <c r="N243" s="40" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="O243" s="35" t="str">
         <f>IFERROR(VLOOKUP($G243,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Yoon, Jeongho</v>
       </c>
       <c r="P243" s="35" t="s">
+        <v>2262</v>
+      </c>
+      <c r="Q243" s="35" t="s">
         <v>2263</v>
-      </c>
-      <c r="Q243" s="35" t="s">
-        <v>2264</v>
       </c>
       <c r="R243" s="35" t="str">
         <f>IFERROR(VLOOKUP($I243,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42514,17 +42510,17 @@
       </c>
       <c r="M244" s="44"/>
       <c r="N244" s="40" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="O244" s="35" t="str">
         <f>IFERROR(VLOOKUP($G244,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Cho, Kongjang</v>
       </c>
       <c r="P244" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="Q244" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R244" s="35" t="str">
         <f>IFERROR(VLOOKUP($I244,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42570,14 +42566,14 @@
       </c>
       <c r="M245" s="44"/>
       <c r="N245" s="40" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="O245" s="35" t="str">
         <f>IFERROR(VLOOKUP($G245,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Huicheul</v>
       </c>
       <c r="P245" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q245" s="35"/>
       <c r="R245" s="35" t="str">
@@ -42624,14 +42620,14 @@
       </c>
       <c r="M246" s="44"/>
       <c r="N246" s="40" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="O246" s="35" t="str">
         <f>IFERROR(VLOOKUP($G246,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P246" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q246" s="35"/>
       <c r="R246" s="35" t="str">
@@ -42678,17 +42674,17 @@
       </c>
       <c r="M247" s="44"/>
       <c r="N247" s="40" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="O247" s="35" t="str">
         <f>IFERROR(VLOOKUP($G247,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P247" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q247" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R247" s="35" t="str">
         <f>IFERROR(VLOOKUP($I247,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42734,17 +42730,17 @@
       </c>
       <c r="M248" s="44"/>
       <c r="N248" s="40" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="O248" s="35" t="str">
         <f>IFERROR(VLOOKUP($G248,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Ryu, Jaena</v>
       </c>
       <c r="P248" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q248" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R248" s="35" t="str">
         <f>IFERROR(VLOOKUP($I248,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42790,14 +42786,14 @@
       </c>
       <c r="M249" s="44"/>
       <c r="N249" s="40" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="O249" s="35" t="str">
         <f>IFERROR(VLOOKUP($G249,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Yi, Sora </v>
       </c>
       <c r="P249" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q249" s="35"/>
       <c r="R249" s="35" t="str">
@@ -42844,17 +42840,17 @@
       </c>
       <c r="M250" s="44"/>
       <c r="N250" s="40" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="O250" s="35" t="str">
         <f>IFERROR(VLOOKUP($G250,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Who-Seung</v>
       </c>
       <c r="P250" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q250" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R250" s="35" t="str">
         <f>IFERROR(VLOOKUP($I250,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42900,17 +42896,17 @@
       </c>
       <c r="M251" s="44"/>
       <c r="N251" s="40" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="O251" s="35" t="str">
         <f>IFERROR(VLOOKUP($G251,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Taeho</v>
       </c>
       <c r="P251" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q251" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R251" s="35" t="str">
         <f>IFERROR(VLOOKUP($I251,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -42956,17 +42952,17 @@
       </c>
       <c r="M252" s="44"/>
       <c r="N252" s="40" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="O252" s="35" t="str">
         <f>IFERROR(VLOOKUP($G252,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Suh, Yang-won</v>
       </c>
       <c r="P252" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q252" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R252" s="35" t="str">
         <f>IFERROR(VLOOKUP($I252,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43012,14 +43008,14 @@
       </c>
       <c r="M253" s="44"/>
       <c r="N253" s="40" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="O253" s="35" t="str">
         <f>IFERROR(VLOOKUP($G253,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P253" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q253" s="35"/>
       <c r="R253" s="35" t="str">
@@ -43066,14 +43062,14 @@
       </c>
       <c r="M254" s="44"/>
       <c r="N254" s="40" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="O254" s="35" t="str">
         <f>IFERROR(VLOOKUP($G254,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P254" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q254" s="35"/>
       <c r="R254" s="35" t="str">
@@ -43094,7 +43090,7 @@
         <v>287</v>
       </c>
       <c r="D255" s="19" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="E255" s="19"/>
       <c r="F255" s="19" t="s">
@@ -43119,17 +43115,17 @@
         <v>46022</v>
       </c>
       <c r="M255" s="44" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="N255" s="40" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="O255" s="35" t="str">
         <f>IFERROR(VLOOKUP($G255,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Huicheul</v>
       </c>
       <c r="P255" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q255" s="35"/>
       <c r="R255" s="35" t="str">
@@ -43147,10 +43143,10 @@
         <v>727</v>
       </c>
       <c r="C256" s="18" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D256" s="19" t="s">
         <v>2228</v>
-      </c>
-      <c r="D256" s="19" t="s">
-        <v>2229</v>
       </c>
       <c r="E256" s="19"/>
       <c r="F256" s="19" t="s">
@@ -43163,7 +43159,7 @@
         <v>732</v>
       </c>
       <c r="I256" s="19" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="J256" s="20">
         <v>3000000</v>
@@ -43176,21 +43172,21 @@
       </c>
       <c r="M256" s="44"/>
       <c r="N256" s="40" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="O256" s="35" t="str">
         <f>IFERROR(VLOOKUP($G256,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lim, Hyesook</v>
       </c>
       <c r="P256" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q256" s="35"/>
       <c r="R256" s="35" t="s">
+        <v>2254</v>
+      </c>
+      <c r="S256" s="35" t="s">
         <v>2255</v>
-      </c>
-      <c r="S256" s="35" t="s">
-        <v>2256</v>
       </c>
     </row>
     <row r="257" spans="1:19" ht="18" customHeight="1">
@@ -43202,7 +43198,7 @@
         <v>734</v>
       </c>
       <c r="D257" s="19" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="E257" s="19"/>
       <c r="F257" s="19" t="s">
@@ -43215,7 +43211,7 @@
         <v>137</v>
       </c>
       <c r="I257" s="19" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="J257" s="20">
         <v>3000000</v>
@@ -43228,23 +43224,23 @@
       </c>
       <c r="M257" s="44"/>
       <c r="N257" s="40" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="O257" s="35" t="str">
         <f>IFERROR(VLOOKUP($G257,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Heo, Namjoo </v>
       </c>
       <c r="P257" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q257" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R257" s="35" t="s">
+        <v>2256</v>
+      </c>
+      <c r="S257" s="35" t="s">
         <v>2257</v>
-      </c>
-      <c r="S257" s="35" t="s">
-        <v>2258</v>
       </c>
     </row>
     <row r="258" spans="1:19" ht="18" customHeight="1">
@@ -43256,7 +43252,7 @@
         <v>741</v>
       </c>
       <c r="D258" s="19" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="E258" s="19"/>
       <c r="F258" s="19" t="s">
@@ -43282,17 +43278,17 @@
       </c>
       <c r="M258" s="44"/>
       <c r="N258" s="40" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="O258" s="35" t="str">
         <f>IFERROR(VLOOKUP($G258,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Hong, Hyunjung</v>
       </c>
       <c r="P258" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q258" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R258" s="35" t="str">
         <f>IFERROR(VLOOKUP($I258,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43312,7 +43308,7 @@
         <v>743</v>
       </c>
       <c r="D259" s="19" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="E259" s="19"/>
       <c r="F259" s="19" t="s">
@@ -43338,17 +43334,17 @@
       </c>
       <c r="M259" s="44"/>
       <c r="N259" s="40" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="O259" s="35" t="str">
         <f>IFERROR(VLOOKUP($G259,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve"> Lim, Miyoung</v>
       </c>
       <c r="P259" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q259" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="R259" s="35" t="str">
         <f>IFERROR(VLOOKUP($I259,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43368,7 +43364,7 @@
         <v>747</v>
       </c>
       <c r="D260" s="19" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="E260" s="19"/>
       <c r="F260" s="19" t="s">
@@ -43381,7 +43377,7 @@
         <v>750</v>
       </c>
       <c r="I260" s="19" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="J260" s="20">
         <v>3000000</v>
@@ -43394,23 +43390,23 @@
       </c>
       <c r="M260" s="44"/>
       <c r="N260" s="40" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O260" s="35" t="str">
         <f>IFERROR(VLOOKUP($G260,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Kim, Doyeon </v>
       </c>
       <c r="P260" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q260" s="35" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="R260" s="35" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="S260" s="35" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="261" spans="1:19" ht="18" customHeight="1">
@@ -43422,7 +43418,7 @@
         <v>752</v>
       </c>
       <c r="D261" s="19" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="E261" s="19"/>
       <c r="F261" s="19" t="s">
@@ -43435,7 +43431,7 @@
         <v>93</v>
       </c>
       <c r="I261" s="19" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="J261" s="20">
         <v>3000000</v>
@@ -43448,23 +43444,23 @@
       </c>
       <c r="M261" s="44"/>
       <c r="N261" s="40" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="O261" s="35" t="str">
         <f>IFERROR(VLOOKUP($G261,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Mikyoung</v>
       </c>
       <c r="P261" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q261" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R261" s="35" t="s">
+        <v>2259</v>
+      </c>
+      <c r="S261" s="35" t="s">
         <v>2260</v>
-      </c>
-      <c r="S261" s="35" t="s">
-        <v>2261</v>
       </c>
     </row>
     <row r="262" spans="1:19" ht="18" customHeight="1">
@@ -43476,7 +43472,7 @@
         <v>754</v>
       </c>
       <c r="D262" s="19" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="E262" s="19"/>
       <c r="F262" s="19" t="s">
@@ -43489,7 +43485,7 @@
         <v>58</v>
       </c>
       <c r="I262" s="19" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="J262" s="20">
         <v>3000000</v>
@@ -43502,20 +43498,20 @@
       </c>
       <c r="M262" s="44"/>
       <c r="N262" s="40" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="O262" s="35"/>
       <c r="P262" s="35" t="s">
+        <v>1798</v>
+      </c>
+      <c r="Q262" s="35" t="s">
         <v>1799</v>
       </c>
-      <c r="Q262" s="35" t="s">
-        <v>1800</v>
-      </c>
       <c r="R262" s="35" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="S262" s="35" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="263" spans="1:19" ht="18" customHeight="1">
@@ -43524,10 +43520,10 @@
         <v>21</v>
       </c>
       <c r="C263" s="18" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D263" s="19" t="s">
         <v>2244</v>
-      </c>
-      <c r="D263" s="19" t="s">
-        <v>2245</v>
       </c>
       <c r="E263" s="19"/>
       <c r="F263" s="19">
@@ -43552,17 +43548,17 @@
         <v>46387</v>
       </c>
       <c r="M263" s="44" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N263" s="40" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="O263" s="35" t="str">
         <f>IFERROR(VLOOKUP($G263,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Huicheul</v>
       </c>
       <c r="P263" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q263" s="35"/>
       <c r="R263" s="35" t="str">
@@ -43580,10 +43576,10 @@
         <v>21</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="D264" s="42" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E264" s="19"/>
       <c r="F264" s="19" t="s">
@@ -43608,17 +43604,17 @@
         <v>46387</v>
       </c>
       <c r="M264" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N264" s="43" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="O264" s="35" t="str">
         <f>IFERROR(VLOOKUP($G264,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Shin, Jiyoung</v>
       </c>
       <c r="P264" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q264" s="35"/>
       <c r="R264" s="35" t="str">
@@ -43636,10 +43632,10 @@
         <v>21</v>
       </c>
       <c r="C265" s="23" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="D265" s="42" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E265" s="19"/>
       <c r="F265" s="19" t="s">
@@ -43664,17 +43660,17 @@
         <v>46387</v>
       </c>
       <c r="M265" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N265" s="43" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="O265" s="35" t="str">
         <f>IFERROR(VLOOKUP($G265,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Cho, Hanna</v>
       </c>
       <c r="P265" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q265" s="35"/>
       <c r="R265" s="35" t="str">
@@ -43692,10 +43688,10 @@
         <v>21</v>
       </c>
       <c r="C266" s="23" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="D266" s="42" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="E266" s="19"/>
       <c r="F266" s="19" t="s">
@@ -43720,20 +43716,20 @@
         <v>46387</v>
       </c>
       <c r="M266" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N266" s="43" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="O266" s="35" t="str">
         <f>IFERROR(VLOOKUP($G266,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Cho, Hanna</v>
       </c>
       <c r="P266" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q266" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R266" s="35" t="str">
         <f>IFERROR(VLOOKUP($I266,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43750,10 +43746,10 @@
         <v>21</v>
       </c>
       <c r="C267" s="23" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="D267" s="42" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E267" s="19"/>
       <c r="F267" s="19" t="s">
@@ -43778,17 +43774,17 @@
         <v>46387</v>
       </c>
       <c r="M267" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N267" s="43" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="O267" s="35" t="str">
         <f>IFERROR(VLOOKUP($G267,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Huicheul</v>
       </c>
       <c r="P267" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q267" s="35"/>
       <c r="R267" s="35" t="str">
@@ -43806,10 +43802,10 @@
         <v>21</v>
       </c>
       <c r="C268" s="23" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="D268" s="42" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E268" s="19"/>
       <c r="F268" s="19" t="s">
@@ -43834,20 +43830,20 @@
         <v>46387</v>
       </c>
       <c r="M268" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N268" s="43" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="O268" s="35" t="str">
         <f>IFERROR(VLOOKUP($G268,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Yoon, Jeongho</v>
       </c>
       <c r="P268" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q268" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="R268" s="35" t="str">
         <f>IFERROR(VLOOKUP($I268,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43864,10 +43860,10 @@
         <v>21</v>
       </c>
       <c r="C269" s="23" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D269" s="42" t="s">
         <v>1832</v>
-      </c>
-      <c r="D269" s="42" t="s">
-        <v>1833</v>
       </c>
       <c r="E269" s="19"/>
       <c r="F269" s="19" t="s">
@@ -43895,17 +43891,17 @@
         <v>74</v>
       </c>
       <c r="N269" s="43" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="O269" s="35" t="str">
         <f>IFERROR(VLOOKUP($G269,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Chang, Hoon</v>
       </c>
       <c r="P269" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q269" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R269" s="35" t="str">
         <f>IFERROR(VLOOKUP($I269,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43922,10 +43918,10 @@
         <v>21</v>
       </c>
       <c r="C270" s="23" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="D270" s="42" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="E270" s="19"/>
       <c r="F270" s="19" t="s">
@@ -43953,17 +43949,17 @@
         <v>436</v>
       </c>
       <c r="N270" s="43" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="O270" s="35" t="str">
         <f>IFERROR(VLOOKUP($G270,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Hyunno</v>
       </c>
       <c r="P270" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q270" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R270" s="35" t="str">
         <f>IFERROR(VLOOKUP($I270,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -43980,10 +43976,10 @@
         <v>21</v>
       </c>
       <c r="C271" s="23" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D271" s="42" t="s">
         <v>1835</v>
-      </c>
-      <c r="D271" s="42" t="s">
-        <v>1836</v>
       </c>
       <c r="E271" s="19"/>
       <c r="F271" s="19" t="s">
@@ -44011,17 +44007,17 @@
         <v>350</v>
       </c>
       <c r="N271" s="43" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="O271" s="35" t="str">
         <f>IFERROR(VLOOKUP($G271,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Choong-ki</v>
       </c>
       <c r="P271" s="35" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="Q271" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R271" s="35" t="str">
         <f>IFERROR(VLOOKUP($I271,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44038,10 +44034,10 @@
         <v>21</v>
       </c>
       <c r="C272" s="23" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="D272" s="42" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="E272" s="19"/>
       <c r="F272" s="19" t="s">
@@ -44069,17 +44065,17 @@
         <v>436</v>
       </c>
       <c r="N272" s="43" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="O272" s="35" t="str">
         <f>IFERROR(VLOOKUP($G272,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Song, Youngil</v>
       </c>
       <c r="P272" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q272" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R272" s="35" t="str">
         <f>IFERROR(VLOOKUP($I272,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44096,10 +44092,10 @@
         <v>21</v>
       </c>
       <c r="C273" s="23" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D273" s="42" t="s">
         <v>1838</v>
-      </c>
-      <c r="D273" s="42" t="s">
-        <v>1839</v>
       </c>
       <c r="E273" s="19"/>
       <c r="F273" s="19" t="s">
@@ -44127,17 +44123,17 @@
         <v>436</v>
       </c>
       <c r="N273" s="43" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="O273" s="35" t="str">
         <f>IFERROR(VLOOKUP($G273,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Song, Youngil</v>
       </c>
       <c r="P273" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q273" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R273" s="35" t="str">
         <f>IFERROR(VLOOKUP($I273,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44154,10 +44150,10 @@
         <v>21</v>
       </c>
       <c r="C274" s="23" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D274" s="42" t="s">
         <v>1840</v>
-      </c>
-      <c r="D274" s="42" t="s">
-        <v>1841</v>
       </c>
       <c r="E274" s="19"/>
       <c r="F274" s="19" t="s">
@@ -44185,17 +44181,17 @@
         <v>436</v>
       </c>
       <c r="N274" s="43" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="O274" s="35" t="str">
         <f>IFERROR(VLOOKUP($G274,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Ahn, Jongho</v>
       </c>
       <c r="P274" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q274" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R274" s="35" t="str">
         <f>IFERROR(VLOOKUP($I274,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44212,10 +44208,10 @@
         <v>21</v>
       </c>
       <c r="C275" s="23" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D275" s="42" t="s">
         <v>1842</v>
-      </c>
-      <c r="D275" s="42" t="s">
-        <v>1843</v>
       </c>
       <c r="E275" s="19"/>
       <c r="F275" s="19" t="s">
@@ -44243,17 +44239,17 @@
         <v>436</v>
       </c>
       <c r="N275" s="43" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="O275" s="35" t="str">
         <f>IFERROR(VLOOKUP($G275,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Chang, Hoon</v>
       </c>
       <c r="P275" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q275" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R275" s="35" t="str">
         <f>IFERROR(VLOOKUP($I275,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44270,10 +44266,10 @@
         <v>21</v>
       </c>
       <c r="C276" s="23" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D276" s="42" t="s">
         <v>1844</v>
-      </c>
-      <c r="D276" s="42" t="s">
-        <v>1845</v>
       </c>
       <c r="E276" s="19"/>
       <c r="F276" s="19" t="s">
@@ -44301,17 +44297,17 @@
         <v>436</v>
       </c>
       <c r="N276" s="43" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="O276" s="35" t="str">
         <f>IFERROR(VLOOKUP($G276,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Huicheul</v>
       </c>
       <c r="P276" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q276" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R276" s="35" t="str">
         <f>IFERROR(VLOOKUP($I276,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44328,10 +44324,10 @@
         <v>21</v>
       </c>
       <c r="C277" s="23" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D277" s="42" t="s">
         <v>1846</v>
-      </c>
-      <c r="D277" s="42" t="s">
-        <v>1847</v>
       </c>
       <c r="E277" s="19"/>
       <c r="F277" s="19" t="s">
@@ -44359,17 +44355,17 @@
         <v>436</v>
       </c>
       <c r="N277" s="43" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="O277" s="35" t="str">
         <f>IFERROR(VLOOKUP($G277,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Jung, Dawoon </v>
       </c>
       <c r="P277" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q277" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R277" s="35" t="str">
         <f>IFERROR(VLOOKUP($I277,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44386,10 +44382,10 @@
         <v>21</v>
       </c>
       <c r="C278" s="23" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D278" s="42" t="s">
         <v>1848</v>
-      </c>
-      <c r="D278" s="42" t="s">
-        <v>1849</v>
       </c>
       <c r="E278" s="19"/>
       <c r="F278" s="19" t="s">
@@ -44417,17 +44413,17 @@
         <v>436</v>
       </c>
       <c r="N278" s="43" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="O278" s="35" t="str">
         <f>IFERROR(VLOOKUP($G278,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Moonhwan</v>
       </c>
       <c r="P278" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q278" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R278" s="35" t="str">
         <f>IFERROR(VLOOKUP($I278,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44444,10 +44440,10 @@
         <v>21</v>
       </c>
       <c r="C279" s="23" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D279" s="42" t="s">
         <v>1850</v>
-      </c>
-      <c r="D279" s="42" t="s">
-        <v>1851</v>
       </c>
       <c r="E279" s="19"/>
       <c r="F279" s="19" t="s">
@@ -44475,17 +44471,17 @@
         <v>436</v>
       </c>
       <c r="N279" s="43" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="O279" s="35" t="str">
         <f>IFERROR(VLOOKUP($G279,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Myeong, Soojeong</v>
       </c>
       <c r="P279" s="35" t="s">
+        <v>1799</v>
+      </c>
+      <c r="Q279" s="35" t="s">
         <v>1800</v>
-      </c>
-      <c r="Q279" s="35" t="s">
-        <v>1801</v>
       </c>
       <c r="R279" s="35" t="str">
         <f>IFERROR(VLOOKUP($I279,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44502,10 +44498,10 @@
         <v>21</v>
       </c>
       <c r="C280" s="23" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D280" s="42" t="s">
         <v>1852</v>
-      </c>
-      <c r="D280" s="42" t="s">
-        <v>1853</v>
       </c>
       <c r="E280" s="19"/>
       <c r="F280" s="19" t="s">
@@ -44533,17 +44529,17 @@
         <v>387</v>
       </c>
       <c r="N280" s="43" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="O280" s="35" t="str">
         <f>IFERROR(VLOOKUP($G280,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Moonhwan</v>
       </c>
       <c r="P280" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q280" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R280" s="35" t="str">
         <f>IFERROR(VLOOKUP($I280,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44560,10 +44556,10 @@
         <v>21</v>
       </c>
       <c r="C281" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D281" s="42" t="s">
         <v>1854</v>
-      </c>
-      <c r="D281" s="42" t="s">
-        <v>1855</v>
       </c>
       <c r="E281" s="19"/>
       <c r="F281" s="19" t="s">
@@ -44591,17 +44587,17 @@
         <v>436</v>
       </c>
       <c r="N281" s="43" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="O281" s="35" t="str">
         <f>IFERROR(VLOOKUP($G281,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Myeong, Soojeong</v>
       </c>
       <c r="P281" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q281" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R281" s="35" t="str">
         <f>IFERROR(VLOOKUP($I281,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44618,10 +44614,10 @@
         <v>21</v>
       </c>
       <c r="C282" s="23" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D282" s="42" t="s">
         <v>1856</v>
-      </c>
-      <c r="D282" s="42" t="s">
-        <v>1857</v>
       </c>
       <c r="E282" s="19"/>
       <c r="F282" s="19" t="s">
@@ -44649,17 +44645,17 @@
         <v>350</v>
       </c>
       <c r="N282" s="43" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="O282" s="35" t="str">
         <f>IFERROR(VLOOKUP($G282,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Taeyun</v>
       </c>
       <c r="P282" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q282" s="35" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="R282" s="35" t="str">
         <f>IFERROR(VLOOKUP($I282,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44676,10 +44672,10 @@
         <v>21</v>
       </c>
       <c r="C283" s="23" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="D283" s="42" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="E283" s="19"/>
       <c r="F283" s="19" t="s">
@@ -44707,17 +44703,17 @@
         <v>436</v>
       </c>
       <c r="N283" s="43" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="O283" s="35" t="str">
         <f>IFERROR(VLOOKUP($G283,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Seungmin</v>
       </c>
       <c r="P283" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q283" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R283" s="35" t="str">
         <f>IFERROR(VLOOKUP($I283,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44734,10 +44730,10 @@
         <v>21</v>
       </c>
       <c r="C284" s="23" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D284" s="42" t="s">
         <v>1859</v>
-      </c>
-      <c r="D284" s="42" t="s">
-        <v>1860</v>
       </c>
       <c r="E284" s="19"/>
       <c r="F284" s="19" t="s">
@@ -44765,17 +44761,17 @@
         <v>436</v>
       </c>
       <c r="N284" s="43" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="O284" s="35" t="str">
         <f>IFERROR(VLOOKUP($G284,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Mikyoung</v>
       </c>
       <c r="P284" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q284" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R284" s="35" t="str">
         <f>IFERROR(VLOOKUP($I284,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44792,10 +44788,10 @@
         <v>21</v>
       </c>
       <c r="C285" s="23" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D285" s="42" t="s">
         <v>1861</v>
-      </c>
-      <c r="D285" s="42" t="s">
-        <v>1862</v>
       </c>
       <c r="E285" s="19"/>
       <c r="F285" s="19" t="s">
@@ -44823,17 +44819,17 @@
         <v>436</v>
       </c>
       <c r="N285" s="43" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="O285" s="35" t="str">
         <f>IFERROR(VLOOKUP($G285,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kang, Hyeongsik</v>
       </c>
       <c r="P285" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q285" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R285" s="35" t="str">
         <f>IFERROR(VLOOKUP($I285,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44850,10 +44846,10 @@
         <v>21</v>
       </c>
       <c r="C286" s="23" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D286" s="42" t="s">
         <v>1863</v>
-      </c>
-      <c r="D286" s="42" t="s">
-        <v>1864</v>
       </c>
       <c r="E286" s="19"/>
       <c r="F286" s="19" t="s">
@@ -44881,17 +44877,17 @@
         <v>449</v>
       </c>
       <c r="N286" s="43" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="O286" s="35" t="str">
         <f>IFERROR(VLOOKUP($G286,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Myeong, Soojeong</v>
       </c>
       <c r="P286" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q286" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R286" s="35" t="str">
         <f>IFERROR(VLOOKUP($I286,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44908,17 +44904,17 @@
         <v>21</v>
       </c>
       <c r="C287" s="23" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D287" s="42" t="s">
         <v>1865</v>
-      </c>
-      <c r="D287" s="42" t="s">
-        <v>1866</v>
       </c>
       <c r="E287" s="19"/>
       <c r="F287" s="19" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G287" s="23" t="s">
         <v>1867</v>
-      </c>
-      <c r="G287" s="23" t="s">
-        <v>1868</v>
       </c>
       <c r="H287" s="19" t="s">
         <v>243</v>
@@ -44939,17 +44935,17 @@
         <v>350</v>
       </c>
       <c r="N287" s="43" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="O287" s="35" t="str">
         <f>IFERROR(VLOOKUP($G287,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jeong, Yunsun</v>
       </c>
       <c r="P287" s="35" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="Q287" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="R287" s="35" t="str">
         <f>IFERROR(VLOOKUP($I287,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -44966,10 +44962,10 @@
         <v>21</v>
       </c>
       <c r="C288" s="23" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D288" s="42" t="s">
         <v>1869</v>
-      </c>
-      <c r="D288" s="42" t="s">
-        <v>1870</v>
       </c>
       <c r="E288" s="19"/>
       <c r="F288" s="19" t="s">
@@ -44997,17 +44993,17 @@
         <v>350</v>
       </c>
       <c r="N288" s="43" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="O288" s="35" t="str">
         <f>IFERROR(VLOOKUP($G288,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Koo, Kyung Ah </v>
       </c>
       <c r="P288" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q288" s="35" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="R288" s="35" t="str">
         <f>IFERROR(VLOOKUP($I288,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45024,10 +45020,10 @@
         <v>21</v>
       </c>
       <c r="C289" s="23" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D289" s="42" t="s">
         <v>1871</v>
-      </c>
-      <c r="D289" s="42" t="s">
-        <v>1872</v>
       </c>
       <c r="E289" s="19"/>
       <c r="F289" s="19" t="s">
@@ -45055,17 +45051,17 @@
         <v>436</v>
       </c>
       <c r="N289" s="43" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="O289" s="35" t="str">
         <f>IFERROR(VLOOKUP($G289,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Hyunno</v>
       </c>
       <c r="P289" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q289" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R289" s="35" t="str">
         <f>IFERROR(VLOOKUP($I289,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45082,10 +45078,10 @@
         <v>21</v>
       </c>
       <c r="C290" s="23" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D290" s="42" t="s">
         <v>1873</v>
-      </c>
-      <c r="D290" s="42" t="s">
-        <v>1874</v>
       </c>
       <c r="E290" s="19"/>
       <c r="F290" s="19" t="s">
@@ -45113,17 +45109,17 @@
         <v>436</v>
       </c>
       <c r="N290" s="43" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="O290" s="35" t="str">
         <f>IFERROR(VLOOKUP($G290,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Chae, Yeora</v>
       </c>
       <c r="P290" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q290" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R290" s="35" t="str">
         <f>IFERROR(VLOOKUP($I290,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45140,10 +45136,10 @@
         <v>21</v>
       </c>
       <c r="C291" s="23" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D291" s="42" t="s">
         <v>1875</v>
-      </c>
-      <c r="D291" s="42" t="s">
-        <v>1876</v>
       </c>
       <c r="E291" s="19"/>
       <c r="F291" s="19" t="s">
@@ -45171,17 +45167,17 @@
         <v>387</v>
       </c>
       <c r="N291" s="43" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="O291" s="35" t="str">
         <f>IFERROR(VLOOKUP($G291,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Song, Jiyoon </v>
       </c>
       <c r="P291" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q291" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R291" s="35" t="str">
         <f>IFERROR(VLOOKUP($I291,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45198,10 +45194,10 @@
         <v>21</v>
       </c>
       <c r="C292" s="23" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D292" s="42" t="s">
         <v>1877</v>
-      </c>
-      <c r="D292" s="42" t="s">
-        <v>1878</v>
       </c>
       <c r="E292" s="19"/>
       <c r="F292" s="19" t="s">
@@ -45229,14 +45225,14 @@
         <v>387</v>
       </c>
       <c r="N292" s="43" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="O292" s="35" t="str">
         <f>IFERROR(VLOOKUP($G292,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Lee, Seungsoo </v>
       </c>
       <c r="P292" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q292" s="35"/>
       <c r="R292" s="35" t="str">
@@ -45254,10 +45250,10 @@
         <v>21</v>
       </c>
       <c r="C293" s="23" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D293" s="42" t="s">
         <v>1879</v>
-      </c>
-      <c r="D293" s="42" t="s">
-        <v>1880</v>
       </c>
       <c r="E293" s="19"/>
       <c r="F293" s="19" t="s">
@@ -45285,17 +45281,17 @@
         <v>436</v>
       </c>
       <c r="N293" s="43" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="O293" s="35" t="str">
         <f>IFERROR(VLOOKUP($G293,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Han, Jihyun </v>
       </c>
       <c r="P293" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q293" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R293" s="35" t="str">
         <f>IFERROR(VLOOKUP($I293,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45312,10 +45308,10 @@
         <v>21</v>
       </c>
       <c r="C294" s="23" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D294" s="42" t="s">
         <v>1881</v>
-      </c>
-      <c r="D294" s="42" t="s">
-        <v>1882</v>
       </c>
       <c r="E294" s="19"/>
       <c r="F294" s="19" t="s">
@@ -45343,17 +45339,17 @@
         <v>375</v>
       </c>
       <c r="N294" s="43" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="O294" s="35" t="str">
         <f>IFERROR(VLOOKUP($G294,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Kim, Geunhan </v>
       </c>
       <c r="P294" s="35" t="s">
+        <v>2261</v>
+      </c>
+      <c r="Q294" s="35" t="s">
         <v>2262</v>
-      </c>
-      <c r="Q294" s="35" t="s">
-        <v>2263</v>
       </c>
       <c r="R294" s="35" t="str">
         <f>IFERROR(VLOOKUP($I294,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45370,10 +45366,10 @@
         <v>21</v>
       </c>
       <c r="C295" s="23" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D295" s="42" t="s">
         <v>1883</v>
-      </c>
-      <c r="D295" s="42" t="s">
-        <v>1884</v>
       </c>
       <c r="E295" s="19"/>
       <c r="F295" s="19" t="s">
@@ -45401,17 +45397,17 @@
         <v>59</v>
       </c>
       <c r="N295" s="43" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="O295" s="35" t="str">
         <f>IFERROR(VLOOKUP($G295,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Yuyoung</v>
       </c>
       <c r="P295" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q295" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R295" s="35" t="str">
         <f>IFERROR(VLOOKUP($I295,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45428,10 +45424,10 @@
         <v>21</v>
       </c>
       <c r="C296" s="23" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D296" s="42" t="s">
         <v>1885</v>
-      </c>
-      <c r="D296" s="42" t="s">
-        <v>1886</v>
       </c>
       <c r="E296" s="19"/>
       <c r="F296" s="19" t="s">
@@ -45459,17 +45455,17 @@
         <v>543</v>
       </c>
       <c r="N296" s="43" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="O296" s="35" t="str">
         <f>IFERROR(VLOOKUP($G296,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Kim, Geunhan </v>
       </c>
       <c r="P296" s="35" t="s">
+        <v>2262</v>
+      </c>
+      <c r="Q296" s="35" t="s">
         <v>2263</v>
-      </c>
-      <c r="Q296" s="35" t="s">
-        <v>2264</v>
       </c>
       <c r="R296" s="35" t="str">
         <f>IFERROR(VLOOKUP($I296,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45486,10 +45482,10 @@
         <v>21</v>
       </c>
       <c r="C297" s="23" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D297" s="42" t="s">
         <v>1887</v>
-      </c>
-      <c r="D297" s="42" t="s">
-        <v>1888</v>
       </c>
       <c r="E297" s="19"/>
       <c r="F297" s="19" t="s">
@@ -45517,14 +45513,14 @@
         <v>649</v>
       </c>
       <c r="N297" s="43" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="O297" s="35" t="str">
         <f>IFERROR(VLOOKUP($G297,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Lee, Seungsoo </v>
       </c>
       <c r="P297" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q297" s="35"/>
       <c r="R297" s="35" t="str">
@@ -45542,10 +45538,10 @@
         <v>21</v>
       </c>
       <c r="C298" s="23" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D298" s="42" t="s">
         <v>1892</v>
-      </c>
-      <c r="D298" s="42" t="s">
-        <v>1893</v>
       </c>
       <c r="E298" s="19"/>
       <c r="F298" s="19" t="s">
@@ -45573,17 +45569,17 @@
         <v>618</v>
       </c>
       <c r="N298" s="43" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="O298" s="35" t="str">
         <f>IFERROR(VLOOKUP($G298,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kang, Sungwon</v>
       </c>
       <c r="P298" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q298" s="35" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="R298" s="35" t="str">
         <f>IFERROR(VLOOKUP($I298,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45600,10 +45596,10 @@
         <v>21</v>
       </c>
       <c r="C299" s="23" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="D299" s="42" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E299" s="19"/>
       <c r="F299" s="19" t="s">
@@ -45631,17 +45627,17 @@
         <v>436</v>
       </c>
       <c r="N299" s="43" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="O299" s="35" t="str">
         <f>IFERROR(VLOOKUP($G299,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Hyun, Yunjung</v>
       </c>
       <c r="P299" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q299" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R299" s="35" t="str">
         <f>IFERROR(VLOOKUP($I299,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45658,10 +45654,10 @@
         <v>21</v>
       </c>
       <c r="C300" s="23" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D300" s="42" t="s">
         <v>1895</v>
-      </c>
-      <c r="D300" s="42" t="s">
-        <v>1896</v>
       </c>
       <c r="E300" s="19"/>
       <c r="F300" s="19" t="s">
@@ -45686,20 +45682,20 @@
         <v>46387</v>
       </c>
       <c r="M300" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N300" s="43" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="O300" s="35" t="str">
         <f>IFERROR(VLOOKUP($G300,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Bae, Hyun-Joo</v>
       </c>
       <c r="P300" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q300" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R300" s="35" t="str">
         <f>IFERROR(VLOOKUP($I300,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45716,7 +45712,7 @@
         <v>797</v>
       </c>
       <c r="C301" s="23" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="D301" s="42" t="s">
         <v>799</v>
@@ -45745,14 +45741,14 @@
       </c>
       <c r="M301" s="19"/>
       <c r="N301" s="43" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="O301" s="35" t="str">
         <f>IFERROR(VLOOKUP($G301,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Jun Hyun</v>
       </c>
       <c r="P301" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q301" s="35"/>
       <c r="R301" s="35" t="str">
@@ -45770,7 +45766,7 @@
         <v>797</v>
       </c>
       <c r="C302" s="23" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="D302" s="42" t="s">
         <v>804</v>
@@ -45799,17 +45795,17 @@
       </c>
       <c r="M302" s="19"/>
       <c r="N302" s="43" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="O302" s="35" t="str">
         <f>IFERROR(VLOOKUP($G302,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Yoon, Jeongho</v>
       </c>
       <c r="P302" s="35" t="s">
+        <v>2262</v>
+      </c>
+      <c r="Q302" s="35" t="s">
         <v>2263</v>
-      </c>
-      <c r="Q302" s="35" t="s">
-        <v>2264</v>
       </c>
       <c r="R302" s="35" t="str">
         <f>IFERROR(VLOOKUP($I302,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45826,7 +45822,7 @@
         <v>797</v>
       </c>
       <c r="C303" s="23" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="D303" s="42" t="s">
         <v>807</v>
@@ -45855,17 +45851,17 @@
       </c>
       <c r="M303" s="19"/>
       <c r="N303" s="43" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="O303" s="35" t="str">
         <f>IFERROR(VLOOKUP($G303,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Dokyun</v>
       </c>
       <c r="P303" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="Q303" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R303" s="35" t="str">
         <f>IFERROR(VLOOKUP($I303,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -45882,7 +45878,7 @@
         <v>797</v>
       </c>
       <c r="C304" s="23" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="D304" s="42" t="s">
         <v>810</v>
@@ -45911,14 +45907,14 @@
       </c>
       <c r="M304" s="19"/>
       <c r="N304" s="43" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="O304" s="35" t="str">
         <f>IFERROR(VLOOKUP($G304,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jung, Huicheul</v>
       </c>
       <c r="P304" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q304" s="35"/>
       <c r="R304" s="35" t="str">
@@ -45936,7 +45932,7 @@
         <v>797</v>
       </c>
       <c r="C305" s="23" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="D305" s="42" t="s">
         <v>813</v>
@@ -45965,14 +45961,14 @@
       </c>
       <c r="M305" s="19"/>
       <c r="N305" s="43" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="O305" s="35" t="str">
         <f>IFERROR(VLOOKUP($G305,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P305" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q305" s="35"/>
       <c r="R305" s="35" t="str">
@@ -45990,7 +45986,7 @@
         <v>797</v>
       </c>
       <c r="C306" s="23" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="D306" s="42" t="s">
         <v>815</v>
@@ -46019,17 +46015,17 @@
       </c>
       <c r="M306" s="19"/>
       <c r="N306" s="43" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="O306" s="35" t="str">
         <f>IFERROR(VLOOKUP($G306,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P306" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q306" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R306" s="35" t="str">
         <f>IFERROR(VLOOKUP($I306,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46046,7 +46042,7 @@
         <v>797</v>
       </c>
       <c r="C307" s="23" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D307" s="42" t="s">
         <v>822</v>
@@ -46075,17 +46071,17 @@
       </c>
       <c r="M307" s="19"/>
       <c r="N307" s="43" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="O307" s="35" t="str">
         <f>IFERROR(VLOOKUP($G307,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Ryu, Jaena</v>
       </c>
       <c r="P307" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q307" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R307" s="35" t="str">
         <f>IFERROR(VLOOKUP($I307,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46102,7 +46098,7 @@
         <v>797</v>
       </c>
       <c r="C308" s="23" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D308" s="42" t="s">
         <v>824</v>
@@ -46131,14 +46127,14 @@
       </c>
       <c r="M308" s="19"/>
       <c r="N308" s="43" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="O308" s="35" t="str">
         <f>IFERROR(VLOOKUP($G308,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Yi, Sora </v>
       </c>
       <c r="P308" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q308" s="35"/>
       <c r="R308" s="35" t="str">
@@ -46156,7 +46152,7 @@
         <v>797</v>
       </c>
       <c r="C309" s="23" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D309" s="42" t="s">
         <v>826</v>
@@ -46185,17 +46181,17 @@
       </c>
       <c r="M309" s="19"/>
       <c r="N309" s="43" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="O309" s="35" t="str">
         <f>IFERROR(VLOOKUP($G309,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Who-Seung</v>
       </c>
       <c r="P309" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q309" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R309" s="35" t="str">
         <f>IFERROR(VLOOKUP($I309,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46212,7 +46208,7 @@
         <v>797</v>
       </c>
       <c r="C310" s="23" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D310" s="42" t="s">
         <v>829</v>
@@ -46241,17 +46237,17 @@
       </c>
       <c r="M310" s="19"/>
       <c r="N310" s="43" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="O310" s="35" t="str">
         <f>IFERROR(VLOOKUP($G310,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Taeho</v>
       </c>
       <c r="P310" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q310" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R310" s="35" t="str">
         <f>IFERROR(VLOOKUP($I310,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46268,10 +46264,10 @@
         <v>797</v>
       </c>
       <c r="C311" s="23" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D311" s="42" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="E311" s="19"/>
       <c r="F311" s="19" t="s">
@@ -46297,17 +46293,17 @@
       </c>
       <c r="M311" s="19"/>
       <c r="N311" s="43" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="O311" s="35" t="str">
         <f>IFERROR(VLOOKUP($G311,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Seungmin</v>
       </c>
       <c r="P311" s="35" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="Q311" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="R311" s="35" t="str">
         <f>IFERROR(VLOOKUP($I311,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46324,10 +46320,10 @@
         <v>797</v>
       </c>
       <c r="C312" s="23" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="D312" s="42" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="E312" s="19"/>
       <c r="F312" s="19" t="s">
@@ -46353,17 +46349,17 @@
       </c>
       <c r="M312" s="19"/>
       <c r="N312" s="43" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="O312" s="35" t="str">
         <f>IFERROR(VLOOKUP($G312,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Taeyun</v>
       </c>
       <c r="P312" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q312" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R312" s="35" t="str">
         <f>IFERROR(VLOOKUP($I312,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46380,7 +46376,7 @@
         <v>797</v>
       </c>
       <c r="C313" s="23" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="D313" s="42" t="s">
         <v>831</v>
@@ -46409,17 +46405,17 @@
       </c>
       <c r="M313" s="19"/>
       <c r="N313" s="43" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="O313" s="35" t="str">
         <f>IFERROR(VLOOKUP($G313,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Suh, Yang-won</v>
       </c>
       <c r="P313" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q313" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R313" s="35" t="str">
         <f>IFERROR(VLOOKUP($I313,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46436,14 +46432,14 @@
         <v>840</v>
       </c>
       <c r="C314" s="23" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D314" s="42" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="E314" s="19"/>
       <c r="F314" s="19" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="G314" s="23" t="s">
         <v>1039</v>
@@ -46465,17 +46461,17 @@
       </c>
       <c r="M314" s="19"/>
       <c r="N314" s="43" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="O314" s="35" t="str">
         <f>IFERROR(VLOOKUP($G314,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Joo, Yong-Joon</v>
       </c>
       <c r="P314" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q314" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R314" s="35" t="str">
         <f>IFERROR(VLOOKUP($I314,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46492,10 +46488,10 @@
         <v>840</v>
       </c>
       <c r="C315" s="23" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="D315" s="42" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="E315" s="19"/>
       <c r="F315" s="19" t="s">
@@ -46521,17 +46517,17 @@
       </c>
       <c r="M315" s="19"/>
       <c r="N315" s="43" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="O315" s="35" t="str">
         <f>IFERROR(VLOOKUP($G315,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Yi, Sora </v>
       </c>
       <c r="P315" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q315" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R315" s="35" t="str">
         <f>IFERROR(VLOOKUP($I315,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46548,10 +46544,10 @@
         <v>840</v>
       </c>
       <c r="C316" s="23" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="D316" s="42" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="E316" s="19"/>
       <c r="F316" s="19" t="s">
@@ -46577,17 +46573,17 @@
       </c>
       <c r="M316" s="19"/>
       <c r="N316" s="43" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="O316" s="35" t="str">
         <f>IFERROR(VLOOKUP($G316,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Hong, Hyunjung</v>
       </c>
       <c r="P316" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q316" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R316" s="35" t="str">
         <f>IFERROR(VLOOKUP($I316,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46604,10 +46600,10 @@
         <v>840</v>
       </c>
       <c r="C317" s="23" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="D317" s="42" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="E317" s="19"/>
       <c r="F317" s="19" t="s">
@@ -46633,17 +46629,17 @@
       </c>
       <c r="M317" s="19"/>
       <c r="N317" s="43" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="O317" s="35" t="str">
         <f>IFERROR(VLOOKUP($G317,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Jung, Dawoon </v>
       </c>
       <c r="P317" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q317" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R317" s="35" t="str">
         <f>IFERROR(VLOOKUP($I317,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46660,10 +46656,10 @@
         <v>840</v>
       </c>
       <c r="C318" s="23" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="D318" s="42" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="E318" s="19"/>
       <c r="F318" s="19" t="s">
@@ -46689,17 +46685,17 @@
       </c>
       <c r="M318" s="19"/>
       <c r="N318" s="43" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="O318" s="35" t="str">
         <f>IFERROR(VLOOKUP($G318,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kang, Hyeongsik</v>
       </c>
       <c r="P318" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q318" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="R318" s="35" t="str">
         <f>IFERROR(VLOOKUP($I318,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46716,14 +46712,14 @@
         <v>840</v>
       </c>
       <c r="C319" s="23" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="D319" s="42" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="E319" s="19"/>
       <c r="F319" s="19" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="G319" s="23" t="s">
         <v>1058</v>
@@ -46745,17 +46741,17 @@
       </c>
       <c r="M319" s="19"/>
       <c r="N319" s="43" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="O319" s="35" t="str">
         <f>IFERROR(VLOOKUP($G319,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Sun, Hyosung</v>
       </c>
       <c r="P319" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q319" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R319" s="35" t="str">
         <f>IFERROR(VLOOKUP($I319,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46772,10 +46768,10 @@
         <v>840</v>
       </c>
       <c r="C320" s="23" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="D320" s="42" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E320" s="19"/>
       <c r="F320" s="19" t="s">
@@ -46801,17 +46797,17 @@
       </c>
       <c r="M320" s="19"/>
       <c r="N320" s="43" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="O320" s="35" t="str">
         <f>IFERROR(VLOOKUP($G320,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Hyungsik</v>
       </c>
       <c r="P320" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q320" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R320" s="35" t="str">
         <f>IFERROR(VLOOKUP($I320,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46828,10 +46824,10 @@
         <v>840</v>
       </c>
       <c r="C321" s="23" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="D321" s="42" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="E321" s="19"/>
       <c r="F321" s="19" t="s">
@@ -46857,14 +46853,14 @@
       </c>
       <c r="M321" s="19"/>
       <c r="N321" s="43" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="O321" s="35" t="str">
         <f>IFERROR(VLOOKUP($G321,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jo, Ji Hye</v>
       </c>
       <c r="P321" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q321" s="35"/>
       <c r="R321" s="35" t="str">
@@ -46882,10 +46878,10 @@
         <v>840</v>
       </c>
       <c r="C322" s="23" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="D322" s="42" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="E322" s="19"/>
       <c r="F322" s="19" t="s">
@@ -46911,14 +46907,14 @@
       </c>
       <c r="M322" s="19"/>
       <c r="N322" s="43" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="O322" s="35" t="str">
         <f>IFERROR(VLOOKUP($G322,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Shin, Jiyoung</v>
       </c>
       <c r="P322" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q322" s="35"/>
       <c r="R322" s="35" t="str">
@@ -46936,17 +46932,17 @@
         <v>840</v>
       </c>
       <c r="C323" s="23" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="D323" s="42" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="E323" s="19"/>
       <c r="F323" s="19" t="s">
+        <v>1934</v>
+      </c>
+      <c r="G323" s="23" t="s">
         <v>1935</v>
-      </c>
-      <c r="G323" s="23" t="s">
-        <v>1936</v>
       </c>
       <c r="H323" s="19" t="s">
         <v>254</v>
@@ -46965,17 +46961,17 @@
       </c>
       <c r="M323" s="19"/>
       <c r="N323" s="43" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="O323" s="35" t="str">
         <f>IFERROR(VLOOKUP($G323,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Jihwan</v>
       </c>
       <c r="P323" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q323" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R323" s="35" t="str">
         <f>IFERROR(VLOOKUP($I323,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -46992,10 +46988,10 @@
         <v>840</v>
       </c>
       <c r="C324" s="23" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="D324" s="42" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="E324" s="19"/>
       <c r="F324" s="19" t="s">
@@ -47021,17 +47017,17 @@
       </c>
       <c r="M324" s="19"/>
       <c r="N324" s="43" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="O324" s="35" t="str">
         <f>IFERROR(VLOOKUP($G324,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Sungjin</v>
       </c>
       <c r="P324" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q324" s="35" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="R324" s="35" t="str">
         <f>IFERROR(VLOOKUP($I324,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47048,10 +47044,10 @@
         <v>840</v>
       </c>
       <c r="C325" s="23" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="D325" s="42" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="E325" s="19"/>
       <c r="F325" s="19" t="s">
@@ -47077,17 +47073,17 @@
       </c>
       <c r="M325" s="19"/>
       <c r="N325" s="43" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="O325" s="35" t="str">
         <f>IFERROR(VLOOKUP($G325,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Park, Juyoung </v>
       </c>
       <c r="P325" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q325" s="46" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="R325" s="35" t="str">
         <f>IFERROR(VLOOKUP($I325,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47104,10 +47100,10 @@
         <v>840</v>
       </c>
       <c r="C326" s="23" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="D326" s="42" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="E326" s="19"/>
       <c r="F326" s="19" t="s">
@@ -47133,14 +47129,14 @@
       </c>
       <c r="M326" s="19"/>
       <c r="N326" s="43" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="O326" s="35" t="str">
         <f>IFERROR(VLOOKUP($G326,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Moonhwan</v>
       </c>
       <c r="P326" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q326" s="35"/>
       <c r="R326" s="35" t="str">
@@ -47158,10 +47154,10 @@
         <v>840</v>
       </c>
       <c r="C327" s="23" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="D327" s="42" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="E327" s="19"/>
       <c r="F327" s="19" t="s">
@@ -47187,17 +47183,17 @@
       </c>
       <c r="M327" s="19"/>
       <c r="N327" s="43" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O327" s="35" t="str">
         <f>IFERROR(VLOOKUP($G327,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Hyo Gyeom</v>
       </c>
       <c r="P327" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q327" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="R327" s="35" t="str">
         <f>IFERROR(VLOOKUP($I327,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47214,10 +47210,10 @@
         <v>840</v>
       </c>
       <c r="C328" s="23" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="D328" s="42" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="E328" s="19"/>
       <c r="F328" s="19" t="s">
@@ -47243,17 +47239,17 @@
       </c>
       <c r="M328" s="19"/>
       <c r="N328" s="43" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="O328" s="35" t="str">
         <f>IFERROR(VLOOKUP($G328,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Heo, Namjoo </v>
       </c>
       <c r="P328" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q328" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R328" s="35" t="str">
         <f>IFERROR(VLOOKUP($I328,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47270,7 +47266,7 @@
         <v>840</v>
       </c>
       <c r="C329" s="23" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="D329" s="42" t="s">
         <v>879</v>
@@ -47299,14 +47295,14 @@
       </c>
       <c r="M329" s="19"/>
       <c r="N329" s="43" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="O329" s="35" t="str">
         <f>IFERROR(VLOOKUP($G329,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P329" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q329" s="35"/>
       <c r="R329" s="35" t="str">
@@ -47324,7 +47320,7 @@
         <v>840</v>
       </c>
       <c r="C330" s="23" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="D330" s="42" t="s">
         <v>881</v>
@@ -47353,14 +47349,14 @@
       </c>
       <c r="M330" s="19"/>
       <c r="N330" s="43" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="O330" s="35" t="str">
         <f>IFERROR(VLOOKUP($G330,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangbum</v>
       </c>
       <c r="P330" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q330" s="35"/>
       <c r="R330" s="35" t="str">
@@ -47378,14 +47374,14 @@
         <v>840</v>
       </c>
       <c r="C331" s="23" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="D331" s="42" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="E331" s="19"/>
       <c r="F331" s="19" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="G331" s="23" t="s">
         <v>1110</v>
@@ -47407,17 +47403,17 @@
       </c>
       <c r="M331" s="19"/>
       <c r="N331" s="43" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="O331" s="35" t="str">
         <f>IFERROR(VLOOKUP($G331,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Shim, Changsub</v>
       </c>
       <c r="P331" s="35" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="Q331" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R331" s="35" t="str">
         <f>IFERROR(VLOOKUP($I331,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47434,10 +47430,10 @@
         <v>836</v>
       </c>
       <c r="C332" s="23" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="D332" s="42" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="E332" s="19"/>
       <c r="F332" s="19" t="s">
@@ -47463,17 +47459,17 @@
       </c>
       <c r="M332" s="19"/>
       <c r="N332" s="43" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="O332" s="35" t="str">
         <f>IFERROR(VLOOKUP($G332,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Hyunno</v>
       </c>
       <c r="P332" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q332" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R332" s="35" t="str">
         <f>IFERROR(VLOOKUP($I332,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47490,10 +47486,10 @@
         <v>836</v>
       </c>
       <c r="C333" s="23" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="D333" s="42" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="E333" s="19"/>
       <c r="F333" s="19" t="s">
@@ -47519,14 +47515,14 @@
       </c>
       <c r="M333" s="19"/>
       <c r="N333" s="47" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="O333" s="35" t="str">
         <f>IFERROR(VLOOKUP($G333,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Jung, Dawoon </v>
       </c>
       <c r="P333" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q333" s="35"/>
       <c r="R333" s="35" t="str">
@@ -47544,10 +47540,10 @@
         <v>836</v>
       </c>
       <c r="C334" s="23" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D334" s="42" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="E334" s="19"/>
       <c r="F334" s="19" t="s">
@@ -47573,17 +47569,17 @@
       </c>
       <c r="M334" s="19"/>
       <c r="N334" s="43" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="O334" s="35" t="str">
         <f>IFERROR(VLOOKUP($G334,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Hee-Sun</v>
       </c>
       <c r="P334" s="35" t="s">
+        <v>2261</v>
+      </c>
+      <c r="Q334" s="35" t="s">
         <v>2262</v>
-      </c>
-      <c r="Q334" s="35" t="s">
-        <v>2263</v>
       </c>
       <c r="R334" s="35" t="str">
         <f>IFERROR(VLOOKUP($I334,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47600,7 +47596,7 @@
         <v>950</v>
       </c>
       <c r="C335" s="23" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="D335" s="42" t="s">
         <v>951</v>
@@ -47629,17 +47625,17 @@
       </c>
       <c r="M335" s="19"/>
       <c r="N335" s="43" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="O335" s="35" t="str">
         <f>IFERROR(VLOOKUP($G335,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Jun Hyun</v>
       </c>
       <c r="P335" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="Q335" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R335" s="35" t="str">
         <f>IFERROR(VLOOKUP($I335,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47656,10 +47652,10 @@
         <v>21</v>
       </c>
       <c r="C336" s="23" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D336" s="42" t="s">
         <v>1889</v>
-      </c>
-      <c r="D336" s="42" t="s">
-        <v>1890</v>
       </c>
       <c r="E336" s="19"/>
       <c r="F336" s="19" t="s">
@@ -47684,20 +47680,20 @@
         <v>46151</v>
       </c>
       <c r="M336" s="19" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="N336" s="43" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="O336" s="35" t="str">
         <f>IFERROR(VLOOKUP($G336,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jo, Ji Hye</v>
       </c>
       <c r="P336" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q336" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R336" s="35" t="str">
         <f>IFERROR(VLOOKUP($I336,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47714,10 +47710,10 @@
         <v>21</v>
       </c>
       <c r="C337" s="23" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="D337" s="42" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="E337" s="19"/>
       <c r="F337" s="19" t="s">
@@ -47745,14 +47741,14 @@
         <v>722</v>
       </c>
       <c r="N337" s="43" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="O337" s="35" t="str">
         <f>IFERROR(VLOOKUP($G337,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Ryu, Jaena</v>
       </c>
       <c r="P337" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q337" s="35"/>
       <c r="R337" s="35" t="str">
@@ -47770,10 +47766,10 @@
         <v>21</v>
       </c>
       <c r="C338" s="23" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="D338" s="42" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="E338" s="19"/>
       <c r="F338" s="19" t="s">
@@ -47798,17 +47794,17 @@
         <v>46368</v>
       </c>
       <c r="M338" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N338" s="43" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="O338" s="35" t="str">
         <f>IFERROR(VLOOKUP($G338,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Seungmin</v>
       </c>
       <c r="P338" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q338" s="35"/>
       <c r="R338" s="35" t="str">
@@ -47826,10 +47822,10 @@
         <v>21</v>
       </c>
       <c r="C339" s="23" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="D339" s="42" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="E339" s="19"/>
       <c r="F339" s="19" t="s">
@@ -47857,14 +47853,14 @@
         <v>286</v>
       </c>
       <c r="N339" s="43" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="O339" s="35" t="str">
         <f>IFERROR(VLOOKUP($G339,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Park, Chang Sug</v>
       </c>
       <c r="P339" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="Q339" s="35"/>
       <c r="R339" s="35" t="str">
@@ -47882,17 +47878,17 @@
         <v>21</v>
       </c>
       <c r="C340" s="23" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="D340" s="42" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="E340" s="19"/>
       <c r="F340" s="19" t="s">
+        <v>1900</v>
+      </c>
+      <c r="G340" s="23" t="s">
         <v>1901</v>
-      </c>
-      <c r="G340" s="23" t="s">
-        <v>1902</v>
       </c>
       <c r="H340" s="19" t="s">
         <v>476</v>
@@ -47910,20 +47906,20 @@
         <v>46387</v>
       </c>
       <c r="M340" s="19" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="N340" s="43" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="O340" s="35" t="str">
         <f>IFERROR(VLOOKUP($G340,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Kim, Dohyeong </v>
       </c>
       <c r="P340" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q340" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R340" s="35" t="str">
         <f>IFERROR(VLOOKUP($I340,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47940,14 +47936,14 @@
         <v>21</v>
       </c>
       <c r="C341" s="23" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="D341" s="42" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="E341" s="19"/>
       <c r="F341" s="19" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="G341" s="23" t="s">
         <v>1246</v>
@@ -47968,20 +47964,20 @@
         <v>46326</v>
       </c>
       <c r="M341" s="19" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="N341" s="43" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="O341" s="35" t="str">
         <f>IFERROR(VLOOKUP($G341,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Lim, Hyungwoo </v>
       </c>
       <c r="P341" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q341" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="R341" s="35" t="str">
         <f>IFERROR(VLOOKUP($I341,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -47998,10 +47994,10 @@
         <v>21</v>
       </c>
       <c r="C342" s="23" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="D342" s="42" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="E342" s="19"/>
       <c r="F342" s="19" t="s">
@@ -48029,17 +48025,17 @@
         <v>631</v>
       </c>
       <c r="N342" s="43" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="O342" s="35" t="str">
         <f>IFERROR(VLOOKUP($G342,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jeon, Dongjin</v>
       </c>
       <c r="P342" s="35" t="s">
+        <v>1802</v>
+      </c>
+      <c r="Q342" s="35" t="s">
         <v>1803</v>
-      </c>
-      <c r="Q342" s="35" t="s">
-        <v>1804</v>
       </c>
       <c r="R342" s="35" t="str">
         <f>IFERROR(VLOOKUP($I342,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48056,10 +48052,10 @@
         <v>953</v>
       </c>
       <c r="C343" s="23" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="D343" s="42" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="E343" s="19"/>
       <c r="F343" s="19" t="s">
@@ -48085,14 +48081,14 @@
       </c>
       <c r="M343" s="19"/>
       <c r="N343" s="43" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="O343" s="35" t="str">
         <f>IFERROR(VLOOKUP($G343,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve"> Lim, Miyoung</v>
       </c>
       <c r="P343" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q343" s="35"/>
       <c r="R343" s="35" t="str">
@@ -48110,10 +48106,10 @@
         <v>953</v>
       </c>
       <c r="C344" s="23" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="D344" s="42" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="E344" s="19"/>
       <c r="F344" s="19" t="s">
@@ -48139,17 +48135,17 @@
       </c>
       <c r="M344" s="19"/>
       <c r="N344" s="43" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="O344" s="35" t="str">
         <f>IFERROR(VLOOKUP($G344,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Ji-Young</v>
       </c>
       <c r="P344" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q344" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R344" s="35" t="str">
         <f>IFERROR(VLOOKUP($I344,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48166,10 +48162,10 @@
         <v>953</v>
       </c>
       <c r="C345" s="23" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="D345" s="42" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="E345" s="19"/>
       <c r="F345" s="19" t="s">
@@ -48195,17 +48191,17 @@
       </c>
       <c r="M345" s="19"/>
       <c r="N345" s="43" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="O345" s="35" t="str">
         <f>IFERROR(VLOOKUP($G345,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Yoonjung</v>
       </c>
       <c r="P345" s="35" t="s">
+        <v>1799</v>
+      </c>
+      <c r="Q345" s="35" t="s">
         <v>1800</v>
-      </c>
-      <c r="Q345" s="35" t="s">
-        <v>1801</v>
       </c>
       <c r="R345" s="35" t="str">
         <f>IFERROR(VLOOKUP($I345,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48222,10 +48218,10 @@
         <v>21</v>
       </c>
       <c r="C346" s="32" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="D346" s="29" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="E346" s="29"/>
       <c r="F346" s="29" t="s">
@@ -48250,20 +48246,20 @@
         <v>47466</v>
       </c>
       <c r="M346" s="29" t="s">
+        <v>2158</v>
+      </c>
+      <c r="N346" s="40" t="s">
         <v>2159</v>
-      </c>
-      <c r="N346" s="40" t="s">
-        <v>2160</v>
       </c>
       <c r="O346" s="35" t="str">
         <f>IFERROR(VLOOKUP($G346,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Cho, Hanna</v>
       </c>
       <c r="P346" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q346" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R346" s="35" t="str">
         <f>IFERROR(VLOOKUP($I346,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48280,10 +48276,10 @@
         <v>21</v>
       </c>
       <c r="C347" s="32" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D347" s="29" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="E347" s="29"/>
       <c r="F347" s="29" t="s">
@@ -48311,17 +48307,17 @@
         <v>350</v>
       </c>
       <c r="N347" s="40" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="O347" s="35" t="str">
         <f>IFERROR(VLOOKUP($G347,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Choong-ki</v>
       </c>
       <c r="P347" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q347" s="35" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="R347" s="35" t="str">
         <f>IFERROR(VLOOKUP($I347,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48338,10 +48334,10 @@
         <v>21</v>
       </c>
       <c r="C348" s="32" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D348" s="29" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="E348" s="29"/>
       <c r="F348" s="29" t="s">
@@ -48369,17 +48365,17 @@
         <v>59</v>
       </c>
       <c r="N348" s="40" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="O348" s="35" t="str">
         <f>IFERROR(VLOOKUP($G348,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Jung, Kichul </v>
       </c>
       <c r="P348" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q348" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R348" s="35" t="str">
         <f>IFERROR(VLOOKUP($I348,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48396,17 +48392,17 @@
         <v>21</v>
       </c>
       <c r="C349" s="32" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D349" s="29" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="E349" s="29"/>
       <c r="F349" s="29" t="s">
+        <v>2131</v>
+      </c>
+      <c r="G349" s="32" t="s">
         <v>2132</v>
-      </c>
-      <c r="G349" s="32" t="s">
-        <v>2133</v>
       </c>
       <c r="H349" s="29" t="s">
         <v>476</v>
@@ -48424,20 +48420,20 @@
         <v>46398</v>
       </c>
       <c r="M349" s="29" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="N349" s="40" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="O349" s="35" t="str">
         <f>IFERROR(VLOOKUP($G349,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Choi, Hyun-Jin </v>
       </c>
       <c r="P349" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q349" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R349" s="35" t="str">
         <f>IFERROR(VLOOKUP($I349,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48454,10 +48450,10 @@
         <v>21</v>
       </c>
       <c r="C350" s="32" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D350" s="29" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="E350" s="29"/>
       <c r="F350" s="29" t="s">
@@ -48482,17 +48478,17 @@
         <v>46356</v>
       </c>
       <c r="M350" s="29" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="N350" s="40" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="O350" s="35" t="str">
         <f>IFERROR(VLOOKUP($G350,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Ahn, Jongho</v>
       </c>
       <c r="P350" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q350" s="35"/>
       <c r="R350" s="35" t="str">
@@ -48510,10 +48506,10 @@
         <v>21</v>
       </c>
       <c r="C351" s="32" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D351" s="29" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="E351" s="29"/>
       <c r="F351" s="29" t="s">
@@ -48538,20 +48534,20 @@
         <v>46350</v>
       </c>
       <c r="M351" s="29" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="N351" s="40" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="O351" s="35" t="str">
         <f>IFERROR(VLOOKUP($G351,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Shin, Dong Won</v>
       </c>
       <c r="P351" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q351" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R351" s="35" t="str">
         <f>IFERROR(VLOOKUP($I351,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48568,10 +48564,10 @@
         <v>21</v>
       </c>
       <c r="C352" s="32" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="D352" s="29" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="E352" s="29"/>
       <c r="F352" s="29" t="s">
@@ -48599,17 +48595,17 @@
         <v>172</v>
       </c>
       <c r="N352" s="40" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="O352" s="35" t="str">
         <f>IFERROR(VLOOKUP($G352,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sunmin</v>
       </c>
       <c r="P352" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q352" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="R352" s="35" t="str">
         <f>IFERROR(VLOOKUP($I352,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48623,13 +48619,13 @@
     <row r="353" spans="1:19" ht="18" customHeight="1">
       <c r="A353" s="31"/>
       <c r="B353" s="32" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C353" s="32" t="s">
         <v>2140</v>
       </c>
-      <c r="C353" s="32" t="s">
-        <v>2141</v>
-      </c>
       <c r="D353" s="29" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="E353" s="29"/>
       <c r="F353" s="29" t="s">
@@ -48655,17 +48651,17 @@
       </c>
       <c r="M353" s="29"/>
       <c r="N353" s="40" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="O353" s="35" t="str">
         <f>IFERROR(VLOOKUP($G353,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Moon, Jongwoo </v>
       </c>
       <c r="P353" s="35" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q353" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R353" s="35" t="str">
         <f>IFERROR(VLOOKUP($I353,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48679,13 +48675,13 @@
     <row r="354" spans="1:19" ht="18" customHeight="1">
       <c r="A354" s="31"/>
       <c r="B354" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C354" s="32" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D354" s="29" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="E354" s="29"/>
       <c r="F354" s="29" t="s">
@@ -48711,17 +48707,17 @@
       </c>
       <c r="M354" s="29"/>
       <c r="N354" s="40" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="O354" s="35" t="str">
         <f>IFERROR(VLOOKUP($G354,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lim, Hyesook</v>
       </c>
       <c r="P354" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q354" s="35" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="R354" s="35" t="str">
         <f>IFERROR(VLOOKUP($I354,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48735,20 +48731,20 @@
     <row r="355" spans="1:19" ht="18" customHeight="1">
       <c r="A355" s="31"/>
       <c r="B355" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C355" s="32" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D355" s="29" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="E355" s="29"/>
       <c r="F355" s="29" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G355" s="32" t="s">
         <v>1867</v>
-      </c>
-      <c r="G355" s="32" t="s">
-        <v>1868</v>
       </c>
       <c r="H355" s="29" t="s">
         <v>243</v>
@@ -48767,14 +48763,14 @@
       </c>
       <c r="M355" s="29"/>
       <c r="N355" s="40" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="O355" s="35" t="str">
         <f>IFERROR(VLOOKUP($G355,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jeong, Yunsun</v>
       </c>
       <c r="P355" s="35" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="Q355" s="35"/>
       <c r="R355" s="35" t="str">
@@ -48789,13 +48785,13 @@
     <row r="356" spans="1:19" ht="18" customHeight="1">
       <c r="A356" s="31"/>
       <c r="B356" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C356" s="32" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="D356" s="29" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="E356" s="29"/>
       <c r="F356" s="29" t="s">
@@ -48821,17 +48817,17 @@
       </c>
       <c r="M356" s="29"/>
       <c r="N356" s="40" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="O356" s="35" t="str">
         <f>IFERROR(VLOOKUP($G356,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Who-Seung</v>
       </c>
       <c r="P356" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q356" s="35" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="R356" s="35" t="str">
         <f>IFERROR(VLOOKUP($I356,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48845,13 +48841,13 @@
     <row r="357" spans="1:19" ht="18" customHeight="1">
       <c r="A357" s="31"/>
       <c r="B357" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C357" s="32" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="D357" s="29" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="E357" s="29"/>
       <c r="F357" s="29" t="s">
@@ -48877,17 +48873,17 @@
       </c>
       <c r="M357" s="29"/>
       <c r="N357" s="40" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="O357" s="35" t="str">
         <f>IFERROR(VLOOKUP($G357,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Ikjae</v>
       </c>
       <c r="P357" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q357" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R357" s="35" t="str">
         <f>IFERROR(VLOOKUP($I357,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48901,13 +48897,13 @@
     <row r="358" spans="1:19" ht="18" customHeight="1">
       <c r="A358" s="31"/>
       <c r="B358" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C358" s="32" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="D358" s="29" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="E358" s="29"/>
       <c r="F358" s="29" t="s">
@@ -48933,17 +48929,17 @@
       </c>
       <c r="M358" s="29"/>
       <c r="N358" s="40" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="O358" s="35" t="str">
         <f>IFERROR(VLOOKUP($G358,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kim, Hojeong</v>
       </c>
       <c r="P358" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q358" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="R358" s="35" t="str">
         <f>IFERROR(VLOOKUP($I358,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -48957,13 +48953,13 @@
     <row r="359" spans="1:19" ht="18" customHeight="1">
       <c r="A359" s="31"/>
       <c r="B359" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C359" s="32" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D359" s="29" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="E359" s="29"/>
       <c r="F359" s="29" t="s">
@@ -48989,17 +48985,17 @@
       </c>
       <c r="M359" s="29"/>
       <c r="N359" s="40" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="O359" s="35" t="str">
         <f>IFERROR(VLOOKUP($G359,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Jeon, Dongjin</v>
       </c>
       <c r="P359" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q359" s="35" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="R359" s="35" t="str">
         <f>IFERROR(VLOOKUP($I359,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -49013,13 +49009,13 @@
     <row r="360" spans="1:19" ht="18" customHeight="1">
       <c r="A360" s="31"/>
       <c r="B360" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C360" s="32" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="D360" s="29" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="E360" s="29"/>
       <c r="F360" s="29" t="s">
@@ -49045,17 +49041,17 @@
       </c>
       <c r="M360" s="29"/>
       <c r="N360" s="40" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="O360" s="35" t="str">
         <f>IFERROR(VLOOKUP($G360,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Choi, Mikyoung</v>
       </c>
       <c r="P360" s="35" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q360" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="R360" s="35" t="str">
         <f>IFERROR(VLOOKUP($I360,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -49069,13 +49065,13 @@
     <row r="361" spans="1:19" ht="18" customHeight="1">
       <c r="A361" s="31"/>
       <c r="B361" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C361" s="32" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="D361" s="29" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="E361" s="29"/>
       <c r="F361" s="29" t="s">
@@ -49101,14 +49097,14 @@
       </c>
       <c r="M361" s="29"/>
       <c r="N361" s="40" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="O361" s="35" t="str">
         <f>IFERROR(VLOOKUP($G361,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Han, Daeho</v>
       </c>
       <c r="P361" s="35" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q361" s="35"/>
       <c r="R361" s="35" t="str">
@@ -49123,13 +49119,13 @@
     <row r="362" spans="1:19" ht="18" customHeight="1">
       <c r="A362" s="31"/>
       <c r="B362" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C362" s="32" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="D362" s="29" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="E362" s="29"/>
       <c r="F362" s="29" t="s">
@@ -49155,14 +49151,14 @@
       </c>
       <c r="M362" s="29"/>
       <c r="N362" s="40" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="O362" s="35" t="str">
         <f>IFERROR(VLOOKUP($G362,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Kim, Taehyun </v>
       </c>
       <c r="P362" s="35" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q362" s="35"/>
       <c r="R362" s="35" t="str">
@@ -49177,13 +49173,13 @@
     <row r="363" spans="1:19" ht="18" customHeight="1">
       <c r="A363" s="31"/>
       <c r="B363" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C363" s="32" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="D363" s="29" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="E363" s="29"/>
       <c r="F363" s="29" t="s">
@@ -49209,17 +49205,17 @@
       </c>
       <c r="M363" s="29"/>
       <c r="N363" s="40" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="O363" s="35" t="str">
         <f>IFERROR(VLOOKUP($G363,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Lee, Sangyun</v>
       </c>
       <c r="P363" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q363" s="35" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="R363" s="35" t="str">
         <f>IFERROR(VLOOKUP($I363,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -49233,13 +49229,13 @@
     <row r="364" spans="1:19" ht="18" customHeight="1">
       <c r="A364" s="31"/>
       <c r="B364" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C364" s="32" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="D364" s="29" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="E364" s="29"/>
       <c r="F364" s="29" t="s">
@@ -49265,17 +49261,17 @@
       </c>
       <c r="M364" s="29"/>
       <c r="N364" s="40" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="O364" s="35" t="str">
         <f>IFERROR(VLOOKUP($G364,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v xml:space="preserve">Heo, Namjoo </v>
       </c>
       <c r="P364" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q364" s="35" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="R364" s="35" t="str">
         <f>IFERROR(VLOOKUP($I364,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -49289,20 +49285,20 @@
     <row r="365" spans="1:19" ht="18" customHeight="1">
       <c r="A365" s="31"/>
       <c r="B365" s="32" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C365" s="32" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="D365" s="29" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="E365" s="29"/>
       <c r="F365" s="29" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G365" s="32" t="s">
         <v>2154</v>
-      </c>
-      <c r="G365" s="32" t="s">
-        <v>2155</v>
       </c>
       <c r="H365" s="29" t="s">
         <v>394</v>
@@ -49321,17 +49317,17 @@
       </c>
       <c r="M365" s="29"/>
       <c r="N365" s="40" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="O365" s="35" t="str">
         <f>IFERROR(VLOOKUP($G365,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
         <v>Kwon, Sunyong</v>
       </c>
       <c r="P365" s="35" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q365" s="35" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="R365" s="35" t="str">
         <f>IFERROR(VLOOKUP($I365,[1]DB2!$F$2:$I$58,2,0),"옛날 부서명 확인")</f>
@@ -49649,10 +49645,10 @@
         <v>1034</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>2113</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>2114</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>2115</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>952</v>
@@ -49689,10 +49685,10 @@
         <v>1038</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>952</v>
@@ -49729,16 +49725,16 @@
         <v>1042</v>
       </c>
       <c r="F14" s="11" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>2119</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>2120</v>
-      </c>
       <c r="H14" s="11" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>2117</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -49749,16 +49745,16 @@
         <v>1044</v>
       </c>
       <c r="F15" s="11" t="s">
+        <v>2120</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>2121</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>2122</v>
-      </c>
       <c r="H15" s="11" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I15" s="11" t="s">
         <v>2117</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>2118</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -49769,10 +49765,10 @@
         <v>1045</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -50244,7 +50240,7 @@
         <v>1105</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="G51" s="11" t="s">
         <v>983</v>
@@ -50286,7 +50282,7 @@
         <v>985</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I53" s="11"/>
     </row>
@@ -50298,7 +50294,7 @@
         <v>1111</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="G54" s="11" t="s">
         <v>986</v>
@@ -50330,10 +50326,10 @@
         <v>1115</v>
       </c>
       <c r="F56" s="45" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="G56" s="45" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -50581,7 +50577,7 @@
         <v>1167</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="88" spans="1:2">

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Desktop\02. 에디터 업무\05. 과제명 영문화\2026\6월_연구진 피드백 받고 재업로드 필요\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3101C0A4-720E-4EFC-A106-A0CB2CF4FE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803A59DB-B990-49C2-9FF2-9A56019A4A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
   </bookViews>
@@ -8733,10 +8733,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Development of Measures to Improve the Contracting System and Operation of Environmental Impact Assessment Services to Enhance System Reliability</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Management of the National Environmental Information Network System</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -8762,6 +8758,10 @@
   </si>
   <si>
     <t>Building an AI-Based Training Dataset for Automatic Wetland Classification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Study on Institutional Improvements and Operational Measures for the Consultant Contracting System to Enhance the Reliability of the Environmental Impact Assessment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22966,7 +22966,7 @@
       </c>
       <c r="C232" s="12" t="str">
         <f>VLOOKUP($A232,'DB1'!$C:$Q,12,0)</f>
-        <v>Development of Measures to Improve the Contracting System and Operation of Environmental Impact Assessment Services to Enhance System Reliability</v>
+        <v>Study on Institutional Improvements and Operational Measures for the Consultant Contracting System to Enhance the Reliability of the Environmental Impact Assessment</v>
       </c>
       <c r="D232" s="11" t="str">
         <f>VLOOKUP($A232,'DB1'!$C:$Q,13,0)</f>
@@ -31619,7 +31619,7 @@
         <v>47</v>
       </c>
       <c r="N10" s="37" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="O10" s="32" t="str">
         <f>IFERROR(VLOOKUP($G10,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -35267,7 +35267,7 @@
         <v>138</v>
       </c>
       <c r="N72" s="37" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="O72" s="32" t="str">
         <f>IFERROR(VLOOKUP($G72,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -42340,7 +42340,7 @@
         <v>649</v>
       </c>
       <c r="N192" s="37" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="O192" s="32" t="str">
         <f>IFERROR(VLOOKUP($G192,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -44459,7 +44459,7 @@
         <v>138</v>
       </c>
       <c r="N228" s="40" t="s">
-        <v>2549</v>
+        <v>2556</v>
       </c>
       <c r="O228" s="32" t="str">
         <f>IFERROR(VLOOKUP($G228,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="M242" s="41"/>
       <c r="N242" s="37" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="O242" s="32" t="str">
         <f>IFERROR(VLOOKUP($G242,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -46640,7 +46640,7 @@
         <v>1810</v>
       </c>
       <c r="N267" s="40" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="O267" s="32" t="str">
         <f>IFERROR(VLOOKUP($G267,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -48320,7 +48320,7 @@
         <v>649</v>
       </c>
       <c r="N296" s="40" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="O296" s="32" t="str">
         <f>IFERROR(VLOOKUP($G296,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -48602,7 +48602,7 @@
       </c>
       <c r="M301" s="16"/>
       <c r="N301" s="40" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="O301" s="32" t="str">
         <f>IFERROR(VLOOKUP($G301,[1]DB2!$A:$B,2,0),"공동과책 확인")</f>
@@ -54410,7 +54410,7 @@
       </c>
       <c r="M405" s="46"/>
       <c r="N405" s="33" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="O405" s="32" t="s">
         <v>2489</v>
